--- a/theme/accessibility/anshilo-accessibility-form.xlsx
+++ b/theme/accessibility/anshilo-accessibility-form.xlsx
@@ -504,14 +504,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
@@ -1091,7 +1091,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עמוד יצירת קשר</t>
         </is>
@@ -1101,7 +1101,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/pages/contact</t>
         </is>
@@ -1116,7 +1116,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -3295,7 +3295,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>התחברות, הרשמה וחשבון לקוח</t>
         </is>
@@ -3305,7 +3305,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/account/login</t>
         </is>
@@ -3320,7 +3320,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -5503,7 +5503,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>בלוג וכתבת בלוג</t>
         </is>
@@ -5513,7 +5513,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/blogs/&lt;דוגמה&gt;</t>
         </is>
@@ -5528,7 +5528,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -7707,7 +7707,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עמוד שגיאה 404</t>
         </is>
@@ -7717,7 +7717,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/404</t>
         </is>
@@ -7732,7 +7732,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -11770,10 +11770,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="74" customHeight="1" s="27">
+    <row r="6" ht="92" customHeight="1" s="27">
       <c r="A6" s="57" t="inlineStr">
         <is>
-          <t>זו בדיקה עצמית מקדימה של קוד התבנית והגדרות החנות, שנועדה לשמש בסיס לבדיקה הרשמית. היא איננה חוות דעת של מורשה נגישות שירות, ואינה מהווה תחליף לה: תקנה 29 מחייבת שההצהרה וההתאמות ייערכו בהתייעצות עם מורשה נגישות שירות, והבדיקה התקופתית לפי תקנה 93(א) (טופס 9) מבוצעת על ידו. את הגיליונות שלהלן יש להעביר למורשה כנקודת פתיחה - הוא יאמת, ישלים את מה שסומן כטרם נבדק, ויחתום.</t>
+          <t>זו בדיקה של קוד התבנית ושל הגדרות החנות, לפי הקריטריונים של הטופס. את הטופס הזה החייב ממלא בעצמו - גיליון ההסבר של הנציבות אינו דורש מורשה נגישות לצורך מילויו, אלא רק לצורך מתן פטור מהתאמה שאינה אפשרית טכנולוגית (ראו שורה D12 בגיליון ההסבר). ההצהרה עצמה מתפרסמת על ידי בעל האתר או מפעילו. מה שאינו יכול להיבדק מתוך הקוד - קורא מסך, מעבר מקלדת, הגדלה ל-200%, מאמת HTML והתבוננות בתמונות - נותר ריק ומופיע ברשימת המשימות שלהלן. מורשה נגישות שירות נדרש לבדיקה התקופתית אחת ל-5 שנים (טופס 9), שהיא מסמך אחר וחלה על השירות כולו ולא על האתר בלבד.</t>
         </is>
       </c>
     </row>
@@ -12347,10 +12347,10 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1" s="27">
-      <c r="A41" s="59" t="inlineStr">
-        <is>
-          <t>•  חוות דעת של מורשה נגישות שירות, כנדרש בתקנה 29, וחתימתו על טופס זה.</t>
+    <row r="41" ht="42" customHeight="1" s="27">
+      <c r="A41" s="69" t="inlineStr">
+        <is>
+          <t>שש המשימות שלמעלה אינן דורשות מורשה נגישות - הן דורשות זמן ואת הכלים החינמיים (NVDA, Lighthouse, WAVE, validator.w3.org). מורשה נגישות שירות נדרש בשני מקרים בלבד: בקשת פטור מהתאמה שאינה אפשרית טכנולוגית, והבדיקה התקופתית אחת ל-5 שנים (טופס 9), שהיא מסמך אחר וחלה על השירות כולו.</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עמוד הבית</t>
         </is>
@@ -12421,7 +12421,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/</t>
         </is>
@@ -12436,7 +12436,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -14619,7 +14619,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עמוד קטגוריה / אוסף מוצרים</t>
         </is>
@@ -14629,7 +14629,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/collections/all</t>
         </is>
@@ -14644,7 +14644,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -16827,7 +16827,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עמוד מוצר</t>
         </is>
@@ -16837,7 +16837,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/products/&lt;דוגמה&gt;</t>
         </is>
@@ -16852,7 +16852,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -19035,7 +19035,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עגלת קניות</t>
         </is>
@@ -19045,7 +19045,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/cart</t>
         </is>
@@ -19060,7 +19060,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -21247,7 +21247,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>תוצאות חיפוש</t>
         </is>
@@ -21257,7 +21257,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/search</t>
         </is>
@@ -21272,7 +21272,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -23455,7 +23455,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עמוד תוכן (מי אנחנו, שאלות ותשובות)</t>
         </is>
@@ -23465,7 +23465,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/pages/&lt;דוגמה&gt;</t>
         </is>
@@ -23480,7 +23480,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -25663,7 +25663,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>עמודי מדיניות, תקנון והצהרת נגישות</t>
         </is>
@@ -25673,7 +25673,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="71" t="inlineStr">
         <is>
           <t>https://anshilo.com/policies/&lt;דוגמה&gt;</t>
         </is>
@@ -25688,7 +25688,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="71" t="inlineStr">
+      <c r="I2" s="69" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>

--- a/theme/accessibility/anshilo-accessibility-form.xlsx
+++ b/theme/accessibility/anshilo-accessibility-form.xlsx
@@ -314,7 +314,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
@@ -464,6 +464,9 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" readingOrder="2"/>
@@ -1091,7 +1094,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עמוד יצירת קשר</t>
         </is>
@@ -1101,7 +1104,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/pages/contact</t>
         </is>
@@ -1116,7 +1119,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -1165,7 +1168,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -1200,7 +1203,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -1215,7 +1218,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -1247,7 +1250,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1262,7 +1265,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -1294,7 +1297,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1309,7 +1312,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -1341,7 +1344,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="76" t="n"/>
+      <c r="F7" s="77" t="n"/>
       <c r="G7" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.1.1</t>
@@ -1352,7 +1355,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>Shopify מוסיפה מנגנון הגנה מפני ספאם לטפסי יצירת קשר, פתיחת חשבון ותגובות בבלוג. זהו רכיב של הפלטפורמה ולא של התבנית, ולכן לא ניתן לאמת מתוך קוד התבנית האם הוא פעיל, האם הוא נגיש והאם קיימת לו חלופה נגישה בחוש אחר. דרוש אימות מול Shopify או בדיקה ידנית בטופס חי - ולכן השורה נותרת ריקה.</t>
         </is>
@@ -1385,7 +1388,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1400,7 +1403,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -1432,7 +1435,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1447,7 +1450,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -1479,7 +1482,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1494,7 +1497,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -1526,7 +1529,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1541,7 +1544,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -1573,7 +1576,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1588,7 +1591,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -1626,7 +1629,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -1641,7 +1644,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -1673,7 +1676,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -1688,7 +1691,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -1720,7 +1723,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -1731,7 +1734,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -1764,7 +1767,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -1779,7 +1782,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -1812,7 +1815,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -1827,7 +1830,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -1859,7 +1862,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -1874,7 +1877,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -1908,7 +1911,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -1923,7 +1926,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -1955,7 +1958,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -1966,7 +1969,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -1998,7 +2001,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -2009,7 +2012,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -2044,7 +2047,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -2055,7 +2058,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -2087,7 +2090,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2102,7 +2105,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -2135,7 +2138,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -2150,7 +2153,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -2183,7 +2186,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2198,7 +2201,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -2230,7 +2233,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2245,7 +2248,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -2277,7 +2280,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2292,7 +2295,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -2324,7 +2327,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2339,7 +2342,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -2371,7 +2374,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -2382,7 +2385,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -2414,7 +2417,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2429,7 +2432,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -2461,7 +2464,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2476,7 +2479,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -2508,7 +2511,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2523,7 +2526,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -2555,7 +2558,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2570,7 +2573,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -2602,7 +2605,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2617,7 +2620,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -2650,7 +2653,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2665,7 +2668,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -2697,7 +2700,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2712,7 +2715,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -2745,7 +2748,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2760,7 +2763,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -2793,7 +2796,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2808,7 +2811,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -2840,7 +2843,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2855,7 +2858,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -2887,7 +2890,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2902,7 +2905,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -2937,7 +2940,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2952,7 +2955,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -2984,7 +2987,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -2999,7 +3002,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -3034,7 +3037,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="73" t="inlineStr">
+      <c r="F43" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -3049,7 +3052,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>שליחת הטופס אינה בלתי הפיכה - אפשר לפנות שוב - ושדות החובה נבדקים לפני השליחה, כך שהמשתמש מקבל הזדמנות לתקן.</t>
         </is>
@@ -3085,7 +3088,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -3096,7 +3099,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -3129,7 +3132,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -3144,7 +3147,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -3295,7 +3298,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>התחברות, הרשמה וחשבון לקוח</t>
         </is>
@@ -3305,7 +3308,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/account/login</t>
         </is>
@@ -3320,7 +3323,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -3369,7 +3372,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -3404,7 +3407,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -3419,7 +3422,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>בעמוד זה אין תמונות תוכן; התמונה היחידה היא הלוגו שבכותרת, הנושא טקסט חלופי. שאר האמור בשורה זו נבדק ברמת התבנית כולה: נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -3451,7 +3454,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -3466,7 +3469,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -3498,7 +3501,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -3513,7 +3516,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -3545,7 +3548,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="76" t="n"/>
+      <c r="F7" s="77" t="n"/>
       <c r="G7" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.1.1</t>
@@ -3556,7 +3559,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>Shopify מוסיפה מנגנון הגנה מפני ספאם לטפסי יצירת קשר, פתיחת חשבון ותגובות בבלוג. זהו רכיב של הפלטפורמה ולא של התבנית, ולכן לא ניתן לאמת מתוך קוד התבנית האם הוא פעיל, האם הוא נגיש והאם קיימת לו חלופה נגישה בחוש אחר. דרוש אימות מול Shopify או בדיקה ידנית בטופס חי - ולכן השורה נותרת ריקה.</t>
         </is>
@@ -3589,7 +3592,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -3604,7 +3607,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -3636,7 +3639,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -3651,7 +3654,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -3683,7 +3686,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -3698,7 +3701,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -3730,7 +3733,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -3745,7 +3748,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -3777,7 +3780,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -3792,7 +3795,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -3830,7 +3833,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -3845,7 +3848,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -3877,7 +3880,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -3892,7 +3895,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -3924,7 +3927,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -3935,7 +3938,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -3968,7 +3971,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -3983,7 +3986,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -4016,7 +4019,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4031,7 +4034,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -4063,7 +4066,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -4078,7 +4081,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -4112,7 +4115,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4127,7 +4130,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -4159,7 +4162,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -4170,7 +4173,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -4202,7 +4205,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="75" t="inlineStr">
+      <c r="F21" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -4217,7 +4220,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה תמונות מלבד הלוגו, הפטור מהקריטריון.</t>
         </is>
@@ -4252,7 +4255,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -4263,7 +4266,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -4295,7 +4298,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4310,7 +4313,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -4343,7 +4346,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -4358,7 +4361,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -4391,7 +4394,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4406,7 +4409,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -4438,7 +4441,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4453,7 +4456,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -4485,7 +4488,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4500,7 +4503,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -4532,7 +4535,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4547,7 +4550,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -4579,7 +4582,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -4590,7 +4593,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -4622,7 +4625,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4637,7 +4640,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -4669,7 +4672,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4684,7 +4687,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -4716,7 +4719,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4731,7 +4734,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -4763,7 +4766,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4778,7 +4781,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -4810,7 +4813,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4825,7 +4828,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -4858,7 +4861,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4873,7 +4876,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -4905,7 +4908,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4920,7 +4923,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -4953,7 +4956,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -4968,7 +4971,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -5001,7 +5004,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5016,7 +5019,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -5048,7 +5051,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5063,7 +5066,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -5095,7 +5098,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5110,7 +5113,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -5145,7 +5148,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5160,7 +5163,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -5192,7 +5195,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5207,7 +5210,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -5242,7 +5245,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="73" t="inlineStr">
+      <c r="F43" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5257,7 +5260,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>נתוני החשבון ניתנים לעריכה ולתיקון לאחר השמירה, ושדות החובה נבדקים לפני השליחה עם הזדמנות לתקן.</t>
         </is>
@@ -5293,7 +5296,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -5304,7 +5307,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -5337,7 +5340,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5352,7 +5355,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -5503,7 +5506,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>בלוג וכתבת בלוג</t>
         </is>
@@ -5513,7 +5516,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/blogs/&lt;דוגמה&gt;</t>
         </is>
@@ -5528,7 +5531,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -5577,7 +5580,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -5612,7 +5615,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -5627,7 +5630,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -5659,7 +5662,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -5674,7 +5677,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. הערה נוספת: גוף עמוד זה נכתב בעורך התוכן של Shopify, שבו אפשר לשבץ נגן חיצוני; נכון למועד הבדיקה לא שובץ נגן כזה.</t>
         </is>
@@ -5706,7 +5709,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -5721,7 +5724,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -5753,7 +5756,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="76" t="n"/>
+      <c r="F7" s="77" t="n"/>
       <c r="G7" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.1.1</t>
@@ -5764,7 +5767,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>Shopify מוסיפה מנגנון הגנה מפני ספאם לטפסי יצירת קשר, פתיחת חשבון ותגובות בבלוג. זהו רכיב של הפלטפורמה ולא של התבנית, ולכן לא ניתן לאמת מתוך קוד התבנית האם הוא פעיל, האם הוא נגיש והאם קיימת לו חלופה נגישה בחוש אחר. דרוש אימות מול Shopify או בדיקה ידנית בטופס חי - ולכן השורה נותרת ריקה.</t>
         </is>
@@ -5797,7 +5800,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -5812,7 +5815,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -5844,7 +5847,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -5859,7 +5862,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -5891,7 +5894,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -5906,7 +5909,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -5938,7 +5941,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -5953,7 +5956,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -5985,7 +5988,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -6000,7 +6003,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -6038,7 +6041,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6053,7 +6056,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -6085,7 +6088,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6100,7 +6103,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -6132,7 +6135,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -6143,7 +6146,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -6176,7 +6179,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6191,7 +6194,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -6224,7 +6227,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6239,7 +6242,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -6271,7 +6274,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -6286,7 +6289,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -6320,7 +6323,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6335,7 +6338,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -6367,7 +6370,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -6378,7 +6381,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -6410,7 +6413,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -6421,7 +6424,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -6456,7 +6459,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -6467,7 +6470,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -6499,7 +6502,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6514,7 +6517,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -6547,7 +6550,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -6562,7 +6565,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -6595,7 +6598,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6610,7 +6613,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -6642,7 +6645,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6657,7 +6660,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -6689,7 +6692,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6704,7 +6707,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -6736,7 +6739,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6751,7 +6754,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -6783,7 +6786,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -6794,7 +6797,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -6826,7 +6829,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6841,7 +6844,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -6873,7 +6876,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6888,7 +6891,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -6920,7 +6923,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6935,7 +6938,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -6967,7 +6970,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -6982,7 +6985,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -7014,7 +7017,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7029,7 +7032,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -7062,7 +7065,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7077,7 +7080,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -7109,7 +7112,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7124,7 +7127,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -7157,7 +7160,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7172,7 +7175,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -7205,7 +7208,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7220,7 +7223,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -7252,7 +7255,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7267,7 +7270,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -7299,7 +7302,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7314,7 +7317,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -7349,7 +7352,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7364,7 +7367,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -7396,7 +7399,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7411,7 +7414,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -7446,7 +7449,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -7461,7 +7464,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -7497,7 +7500,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -7508,7 +7511,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -7541,7 +7544,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7556,7 +7559,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -7707,7 +7710,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עמוד שגיאה 404</t>
         </is>
@@ -7717,7 +7720,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/404</t>
         </is>
@@ -7732,7 +7735,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -7781,7 +7784,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -7816,7 +7819,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -7831,7 +7834,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -7863,7 +7866,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -7878,7 +7881,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -7910,7 +7913,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -7925,7 +7928,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -7957,7 +7960,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -7972,7 +7975,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -8005,7 +8008,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -8020,7 +8023,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -8052,7 +8055,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -8067,7 +8070,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -8099,7 +8102,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -8114,7 +8117,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -8146,7 +8149,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -8161,7 +8164,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -8193,7 +8196,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -8208,7 +8211,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -8246,7 +8249,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8261,7 +8264,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -8293,7 +8296,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8308,7 +8311,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -8340,7 +8343,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -8351,7 +8354,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -8384,7 +8387,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8399,7 +8402,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -8432,7 +8435,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8447,7 +8450,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -8479,7 +8482,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -8494,7 +8497,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -8528,7 +8531,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8543,7 +8546,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -8575,7 +8578,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -8586,7 +8589,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -8618,7 +8621,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -8629,7 +8632,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -8664,7 +8667,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -8675,7 +8678,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -8707,7 +8710,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8722,7 +8725,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -8755,7 +8758,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -8770,7 +8773,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -8803,7 +8806,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8818,7 +8821,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -8850,7 +8853,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8865,7 +8868,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -8897,7 +8900,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8912,7 +8915,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -8944,7 +8947,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -8959,7 +8962,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -8991,7 +8994,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -9002,7 +9005,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -9034,7 +9037,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9049,7 +9052,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -9081,7 +9084,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9096,7 +9099,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -9128,7 +9131,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9143,7 +9146,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -9175,7 +9178,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9190,7 +9193,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -9222,7 +9225,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9237,7 +9240,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -9270,7 +9273,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9285,7 +9288,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -9317,7 +9320,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9332,7 +9335,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -9365,7 +9368,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9380,7 +9383,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -9413,7 +9416,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9428,7 +9431,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -9460,7 +9463,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9475,7 +9478,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -9507,7 +9510,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9522,7 +9525,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -9557,7 +9560,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9572,7 +9575,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -9604,7 +9607,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9619,7 +9622,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -9654,7 +9657,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -9669,7 +9672,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -9705,7 +9708,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -9716,7 +9719,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -9749,7 +9752,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -9764,7 +9767,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -11763,606 +11766,613 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="76" customHeight="1" s="27">
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t>⚠ נושא הבדיקה: ערכת העיצוב "shilov8theme" (מזהה 148378648655), שאיננה מפורסמת. ערכת העיצוב הפומבית במועד הבדיקה היא "שמירה 1" (מזהה 141469646927, עודכנה 28.03.2026) - ערכה אחרת, שאין בה כלל את קבצי התבנית שנבדקו כאן. כל התאמה המתועדת במסמך זה חלה על הערכה שטרם פורסמה, ולא על מה שהציבור רואה כרגע. לפני הגשה יש לפרסם את הערכה שנבדקה, או לבדוק מחדש את הערכה הפומבית - הצהרה על התאמות שאינן באוויר היא בדיוק מה שאין לעשות במסמך המוגש לפי תקנה 93(א).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>מה המסמך הזה, ומה הוא איננו</t>
         </is>
       </c>
     </row>
     <row r="6" ht="92" customHeight="1" s="27">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>זו בדיקה של קוד התבנית ושל הגדרות החנות, לפי הקריטריונים של הטופס. את הטופס הזה החייב ממלא בעצמו - גיליון ההסבר של הנציבות אינו דורש מורשה נגישות לצורך מילויו, אלא רק לצורך מתן פטור מהתאמה שאינה אפשרית טכנולוגית (ראו שורה D12 בגיליון ההסבר). ההצהרה עצמה מתפרסמת על ידי בעל האתר או מפעילו. מה שאינו יכול להיבדק מתוך הקוד - קורא מסך, מעבר מקלדת, הגדלה ל-200%, מאמת HTML והתבוננות בתמונות - נותר ריק ומופיע ברשימת המשימות שלהלן. מורשה נגישות שירות נדרש לבדיקה התקופתית אחת ל-5 שנים (טופס 9), שהיא מסמך אחר וחלה על השירות כולו ולא על האתר בלבד.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="56" t="inlineStr">
+      <c r="A8" s="57" t="inlineStr">
         <is>
           <t>מקרא עמודת "תוצאה"</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" s="27">
-      <c r="A9" s="58" t="inlineStr">
-        <is>
-          <t>תקין</t>
-        </is>
-      </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>תקין</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>נבדק, ונמצא עומד בקריטריון. ההערה בעמודה I מפרטת את הראיה - קובץ ושורה, מדידה, או בדיקה שבוצעה בדפדפן.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" s="27">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>לא תקין</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>נבדק, ונמצא שאינו עומד בקריטריון. לא נותרו כאלה: ארבעה כשלי ניגודיות, כשל בסימון הפוקוס בשדה הכמות וכשל בעצירת התנועה בסרגל ההודעות נמצאו במהלך הבדיקה ותוקנו.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" s="27">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>הקריטריון אינו חל על העמוד - למשל קריטריוני אודיו ווידאו באתר שאין בו מדיה מבוססת זמן. ההערה מסבירה על סמך מה נקבע.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" s="27">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>(ריק)</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>טרם נבדק. הקריטריון דורש בדיקה שלא ניתן לבצע מתוך הקוד: קורא מסך, מעבר מקלדת ידני, הגדלה ל-200%, מאמת HTML, או התבוננות בתמונות עצמן. ההערה אומרת בדיוק מה נבדק ומה נותר. אלה הפריטים שהמורשה צריך להשלים.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="56" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>סיכום לפי עמוד</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="63" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>עמוד / מסמך</t>
         </is>
       </c>
-      <c r="B15" s="64" t="inlineStr">
-        <is>
-          <t>תקין</t>
-        </is>
-      </c>
-      <c r="C15" s="64" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>תקין</t>
+        </is>
+      </c>
+      <c r="C15" s="65" t="inlineStr">
         <is>
           <t>לא תקין</t>
         </is>
       </c>
-      <c r="D15" s="64" t="inlineStr">
+      <c r="D15" s="65" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
       </c>
-      <c r="E15" s="64" t="inlineStr">
+      <c r="E15" s="65" t="inlineStr">
         <is>
           <t>טרם נבדק</t>
         </is>
       </c>
-      <c r="F15" s="64" t="inlineStr">
+      <c r="F15" s="65" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="G15" s="63" t="inlineStr">
+      <c r="G15" s="64" t="inlineStr">
         <is>
           <t>הפריטים שטרם נבדקו</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="27">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>עמוד הבית</t>
         </is>
       </c>
-      <c r="B16" s="65">
+      <c r="B16" s="66">
         <f>COUNTIF('עמוד הבית'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="66">
         <f>COUNTIF('עמוד הבית'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D16" s="65">
+      <c r="D16" s="66">
         <f>COUNTIF('עמוד הבית'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>11</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E16" s="66">
         <f>COUNTBLANK('עמוד הבית'!$F$4:$F$45)</f>
         <v>6</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F16" s="66">
         <f>SUM(B16:E16)</f>
         <v>42</v>
       </c>
-      <c r="G16" s="59" t="inlineStr">
+      <c r="G16" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="27">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>עמוד קטגוריה / אוסף מוצרים</t>
         </is>
       </c>
-      <c r="B17" s="65">
+      <c r="B17" s="66">
         <f>COUNTIF('עמוד קטגוריה'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="66">
         <f>COUNTIF('עמוד קטגוריה'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="66">
         <f>COUNTIF('עמוד קטגוריה'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>11</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="66">
         <f>COUNTBLANK('עמוד קטגוריה'!$F$4:$F$45)</f>
         <v>6</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="66">
         <f>SUM(B17:E17)</f>
         <v>42</v>
       </c>
-      <c r="G17" s="59" t="inlineStr">
+      <c r="G17" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="27">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t>עמוד מוצר</t>
         </is>
       </c>
-      <c r="B18" s="65">
+      <c r="B18" s="66">
         <f>COUNTIF('עמוד מוצר'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C18" s="65">
+      <c r="C18" s="66">
         <f>COUNTIF('עמוד מוצר'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D18" s="65">
+      <c r="D18" s="66">
         <f>COUNTIF('עמוד מוצר'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>11</v>
       </c>
-      <c r="E18" s="65">
+      <c r="E18" s="66">
         <f>COUNTBLANK('עמוד מוצר'!$F$4:$F$45)</f>
         <v>6</v>
       </c>
-      <c r="F18" s="65">
+      <c r="F18" s="66">
         <f>SUM(B18:E18)</f>
         <v>42</v>
       </c>
-      <c r="G18" s="59" t="inlineStr">
+      <c r="G18" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="27">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>עגלת קניות</t>
         </is>
       </c>
-      <c r="B19" s="65">
+      <c r="B19" s="66">
         <f>COUNTIF('עגלת קניות'!$F$4:$F$45,"תקין")</f>
         <v>26</v>
       </c>
-      <c r="C19" s="65">
+      <c r="C19" s="66">
         <f>COUNTIF('עגלת קניות'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D19" s="65">
+      <c r="D19" s="66">
         <f>COUNTIF('עגלת קניות'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>11</v>
       </c>
-      <c r="E19" s="65">
+      <c r="E19" s="66">
         <f>COUNTBLANK('עגלת קניות'!$F$4:$F$45)</f>
         <v>5</v>
       </c>
-      <c r="F19" s="65">
+      <c r="F19" s="66">
         <f>SUM(B19:E19)</f>
         <v>42</v>
       </c>
-      <c r="G19" s="59" t="inlineStr">
+      <c r="G19" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="27">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>תוצאות חיפוש</t>
         </is>
       </c>
-      <c r="B20" s="65">
+      <c r="B20" s="66">
         <f>COUNTIF('תוצאות חיפוש'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="66">
         <f>COUNTIF('תוצאות חיפוש'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D20" s="65">
+      <c r="D20" s="66">
         <f>COUNTIF('תוצאות חיפוש'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>11</v>
       </c>
-      <c r="E20" s="65">
+      <c r="E20" s="66">
         <f>COUNTBLANK('תוצאות חיפוש'!$F$4:$F$45)</f>
         <v>6</v>
       </c>
-      <c r="F20" s="65">
+      <c r="F20" s="66">
         <f>SUM(B20:E20)</f>
         <v>42</v>
       </c>
-      <c r="G20" s="59" t="inlineStr">
+      <c r="G20" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="27">
-      <c r="A21" s="59" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>עמוד תוכן (מי אנחנו, שאלות ותשובות)</t>
         </is>
       </c>
-      <c r="B21" s="65">
+      <c r="B21" s="66">
         <f>COUNTIF('עמוד תוכן'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C21" s="65">
+      <c r="C21" s="66">
         <f>COUNTIF('עמוד תוכן'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="65">
+      <c r="D21" s="66">
         <f>COUNTIF('עמוד תוכן'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>11</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="66">
         <f>COUNTBLANK('עמוד תוכן'!$F$4:$F$45)</f>
         <v>6</v>
       </c>
-      <c r="F21" s="65">
+      <c r="F21" s="66">
         <f>SUM(B21:E21)</f>
         <v>42</v>
       </c>
-      <c r="G21" s="59" t="inlineStr">
+      <c r="G21" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="27">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>עמודי מדיניות, תקנון והצהרת נגישות</t>
         </is>
       </c>
-      <c r="B22" s="65">
+      <c r="B22" s="66">
         <f>COUNTIF('עמודים משפטיים'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C22" s="65">
+      <c r="C22" s="66">
         <f>COUNTIF('עמודים משפטיים'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="66">
         <f>COUNTIF('עמודים משפטיים'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>12</v>
       </c>
-      <c r="E22" s="65">
+      <c r="E22" s="66">
         <f>COUNTBLANK('עמודים משפטיים'!$F$4:$F$45)</f>
         <v>5</v>
       </c>
-      <c r="F22" s="65">
+      <c r="F22" s="66">
         <f>SUM(B22:E22)</f>
         <v>42</v>
       </c>
-      <c r="G22" s="59" t="inlineStr">
+      <c r="G22" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="27">
-      <c r="A23" s="59" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>עמוד יצירת קשר</t>
         </is>
       </c>
-      <c r="B23" s="65">
+      <c r="B23" s="66">
         <f>COUNTIF('יצירת קשר'!$F$4:$F$45,"תקין")</f>
         <v>26</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="66">
         <f>COUNTIF('יצירת קשר'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D23" s="65">
+      <c r="D23" s="66">
         <f>COUNTIF('יצירת קשר'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>9</v>
       </c>
-      <c r="E23" s="65">
+      <c r="E23" s="66">
         <f>COUNTBLANK('יצירת קשר'!$F$4:$F$45)</f>
         <v>7</v>
       </c>
-      <c r="F23" s="65">
+      <c r="F23" s="66">
         <f>SUM(B23:E23)</f>
         <v>42</v>
       </c>
-      <c r="G23" s="59" t="inlineStr">
+      <c r="G23" s="60" t="inlineStr">
         <is>
           <t>1.1.1, 1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="27">
-      <c r="A24" s="59" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>התחברות, הרשמה וחשבון לקוח</t>
         </is>
       </c>
-      <c r="B24" s="65">
+      <c r="B24" s="66">
         <f>COUNTIF('חשבון לקוח'!$F$4:$F$45,"תקין")</f>
         <v>26</v>
       </c>
-      <c r="C24" s="65">
+      <c r="C24" s="66">
         <f>COUNTIF('חשבון לקוח'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D24" s="65">
+      <c r="D24" s="66">
         <f>COUNTIF('חשבון לקוח'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>10</v>
       </c>
-      <c r="E24" s="65">
+      <c r="E24" s="66">
         <f>COUNTBLANK('חשבון לקוח'!$F$4:$F$45)</f>
         <v>6</v>
       </c>
-      <c r="F24" s="65">
+      <c r="F24" s="66">
         <f>SUM(B24:E24)</f>
         <v>42</v>
       </c>
-      <c r="G24" s="59" t="inlineStr">
+      <c r="G24" s="60" t="inlineStr">
         <is>
           <t>1.1.1, 1.3.2, 1.4.4, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="27">
-      <c r="A25" s="59" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>בלוג וכתבת בלוג</t>
         </is>
       </c>
-      <c r="B25" s="65">
+      <c r="B25" s="66">
         <f>COUNTIF('בלוג וכתבה'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="66">
         <f>COUNTIF('בלוג וכתבה'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="65">
+      <c r="D25" s="66">
         <f>COUNTIF('בלוג וכתבה'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>10</v>
       </c>
-      <c r="E25" s="65">
+      <c r="E25" s="66">
         <f>COUNTBLANK('בלוג וכתבה'!$F$4:$F$45)</f>
         <v>7</v>
       </c>
-      <c r="F25" s="65">
+      <c r="F25" s="66">
         <f>SUM(B25:E25)</f>
         <v>42</v>
       </c>
-      <c r="G25" s="59" t="inlineStr">
+      <c r="G25" s="60" t="inlineStr">
         <is>
           <t>1.1.1, 1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="27">
-      <c r="A26" s="59" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>עמוד שגיאה 404</t>
         </is>
       </c>
-      <c r="B26" s="65">
+      <c r="B26" s="66">
         <f>COUNTIF('שגיאה 404'!$F$4:$F$45,"תקין")</f>
         <v>25</v>
       </c>
-      <c r="C26" s="65">
+      <c r="C26" s="66">
         <f>COUNTIF('שגיאה 404'!$F$4:$F$45,"לא תקין")</f>
         <v>0</v>
       </c>
-      <c r="D26" s="65">
+      <c r="D26" s="66">
         <f>COUNTIF('שגיאה 404'!$F$4:$F$45,"לא רלוונטי")</f>
         <v>11</v>
       </c>
-      <c r="E26" s="65">
+      <c r="E26" s="66">
         <f>COUNTBLANK('שגיאה 404'!$F$4:$F$45)</f>
         <v>6</v>
       </c>
-      <c r="F26" s="65">
+      <c r="F26" s="66">
         <f>SUM(B26:E26)</f>
         <v>42</v>
       </c>
-      <c r="G26" s="59" t="inlineStr">
+      <c r="G26" s="60" t="inlineStr">
         <is>
           <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="66" t="inlineStr">
+      <c r="A27" s="67" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B27" s="67">
+      <c r="B27" s="68">
         <f>SUM(B16:B26)</f>
         <v>278</v>
       </c>
-      <c r="C27" s="67">
+      <c r="C27" s="68">
         <f>SUM(C16:C26)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="67">
+      <c r="D27" s="68">
         <f>SUM(D16:D26)</f>
         <v>118</v>
       </c>
-      <c r="E27" s="67">
+      <c r="E27" s="68">
         <f>SUM(E16:E26)</f>
         <v>66</v>
       </c>
-      <c r="F27" s="67">
+      <c r="F27" s="68">
         <f>SUM(F16:F26)</f>
         <v>462</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="56" t="inlineStr">
+      <c r="A29" s="57" t="inlineStr">
         <is>
           <t>מה תוקן במהלך הבדיקה הזו</t>
         </is>
       </c>
     </row>
     <row r="30" ht="44" customHeight="1" s="27">
-      <c r="A30" s="68" t="inlineStr">
+      <c r="A30" s="69" t="inlineStr">
         <is>
           <t>1.4.3 - ניגודיות</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש. הוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בחמש קומפוננטות. נמדדו 36 שילובי צבע; כל השאר עומדים.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="44" customHeight="1" s="27">
-      <c r="A31" s="68" t="inlineStr">
+      <c r="A31" s="69" t="inlineStr">
         <is>
           <t>2.4.7 - פוקוס נראה לעין</t>
         </is>
       </c>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>שדה הכמות ביטל את מסגרת הפוקוס ולא החזיר דבר במקומה, כך שמעבר מקלדת אליו - בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה מהירה - לא הראה שום סימן. הוחזרה מסגרת 2px, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="44" customHeight="1" s="27">
-      <c r="A32" s="68" t="inlineStr">
+      <c r="A32" s="69" t="inlineStr">
         <is>
           <t>2.2.2 - הפסקה, עצירה, הסתרה</t>
         </is>
       </c>
-      <c r="B32" s="59" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>לחצן "עצירת אנימציות ותנועה" שבתפריט הנגישות לא עצר את סרגל ההודעות: גיליון סגנון אינו יכול לעצור טיימר. הסרגל נגזר כיום מבחירת המבקר, מהגדרת הסוחר ומהגדרת מערכת ההפעלה, ונעצר ברגע הלחיצה. אותה סיבה גם מנעה מהלחצן לעצור את אנימציות פתיחת האקורדיון, וגם זה תוקן.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="56" t="inlineStr">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>מה נדרש כדי לסגור את הבדיקה</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1" s="27">
-      <c r="A35" s="59" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>•  בדיקת קורא מסך על כל תבנית עמוד - הטופס מחייב זאת מפורשות בקריטריון 1.3.2.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1" s="27">
-      <c r="A36" s="59" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>•  מעבר מקלדת ידני מלא בכל עמוד, כולל מגירת העגלה, מגירת הסינון, גלריית המוצר וההזמנה המהירה (קריטריונים 2.1.1 ו-2.4.3).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1" s="27">
-      <c r="A37" s="59" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>•  הגדלת התצוגה ל-200% בכל עמוד ואימות שלא נאבד תוכן או פונקציונליות (1.4.4).</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1" s="27">
-      <c r="A38" s="59" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>•  הרצת מאמת HTML של W3C על העמודים כפי שהם מורכבים בפועל (4.1.1).</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1" s="27">
-      <c r="A39" s="59" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>•  התבוננות בתמונות הבאנר והאריחים שהועלו, ואימות שאין בהן טקסט "צרוב" (1.4.5).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1" s="27">
-      <c r="A40" s="59" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>•  אימות מול Shopify של נגישות מנגנון ההגנה מפני ספאם בטפסים, ושל קיום חלופה נגישה (1.1.1 CAPTCHA).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1" s="27">
-      <c r="A41" s="69" t="inlineStr">
+      <c r="A41" s="70" t="inlineStr">
         <is>
           <t>שש המשימות שלמעלה אינן דורשות מורשה נגישות - הן דורשות זמן ואת הכלים החינמיים (NVDA, Lighthouse, WAVE, validator.w3.org). מורשה נגישות שירות נדרש בשני מקרים בלבד: בקשת פטור מהתאמה שאינה אפשרית טכנולוגית, והבדיקה התקופתית אחת ל-5 שנים (טופס 9), שהיא מסמך אחר וחלה על השירות כולו.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="66" t="inlineStr">
+      <c r="A43" s="67" t="inlineStr">
         <is>
           <t>רכז הנגישות: דביר ארליכמן | טלפון 058-455-4333 | דוא"ל info@anshilo.com</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="A40:G40"/>
@@ -12370,10 +12380,11 @@
     <mergeCell ref="B31:G31"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="B9:G9"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="B30:G30"/>
@@ -12411,7 +12422,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עמוד הבית</t>
         </is>
@@ -12421,7 +12432,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/</t>
         </is>
@@ -12436,7 +12447,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -12485,7 +12496,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -12520,7 +12531,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -12535,7 +12546,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -12567,7 +12578,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12582,7 +12593,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -12614,7 +12625,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12629,7 +12640,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -12661,7 +12672,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12676,7 +12687,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -12709,7 +12720,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12724,7 +12735,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -12756,7 +12767,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12771,7 +12782,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -12803,7 +12814,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12818,7 +12829,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -12850,7 +12861,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12865,7 +12876,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -12897,7 +12908,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -12912,7 +12923,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -12950,7 +12961,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -12965,7 +12976,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -12997,7 +13008,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13012,7 +13023,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -13044,7 +13055,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -13055,7 +13066,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -13088,7 +13099,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13103,7 +13114,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -13136,7 +13147,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13151,7 +13162,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -13183,7 +13194,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -13198,7 +13209,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -13232,7 +13243,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13247,7 +13258,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה. באזור התמונה הראשי בעמוד הבית, שבו טקסט מונח על צילום ולכן זהו המקרה המורכב ביותר, נמדדה ניגודיות של 6.7:1 לכל הפחות - הבדיקה בוצעה מול תחליף בהיר מאוד ותחליף כהה מאוד שנבנו במיוחד כדי לתחום את טווח הצילומים האפשרי.</t>
         </is>
@@ -13279,7 +13290,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -13290,7 +13301,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -13322,7 +13333,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -13333,7 +13344,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -13368,7 +13379,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -13379,7 +13390,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -13411,7 +13422,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13426,7 +13437,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -13459,7 +13470,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -13474,7 +13485,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -13507,7 +13518,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13522,7 +13533,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -13554,7 +13565,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13569,7 +13580,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -13601,7 +13612,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13616,7 +13627,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -13648,7 +13659,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13663,7 +13674,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -13695,7 +13706,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -13706,7 +13717,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -13738,7 +13749,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13753,7 +13764,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -13785,7 +13796,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13800,7 +13811,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -13832,7 +13843,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13847,7 +13858,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -13879,7 +13890,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13894,7 +13905,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -13926,7 +13937,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13941,7 +13952,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -13974,7 +13985,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -13989,7 +14000,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -14021,7 +14032,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14036,7 +14047,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -14069,7 +14080,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14084,7 +14095,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -14117,7 +14128,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14132,7 +14143,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -14164,7 +14175,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14179,7 +14190,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -14211,7 +14222,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14226,7 +14237,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -14261,7 +14272,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14276,7 +14287,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -14308,7 +14319,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14323,7 +14334,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -14358,7 +14369,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -14373,7 +14384,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -14409,7 +14420,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -14420,7 +14431,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -14453,7 +14464,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14468,7 +14479,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -14619,7 +14630,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עמוד קטגוריה / אוסף מוצרים</t>
         </is>
@@ -14629,7 +14640,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/collections/all</t>
         </is>
@@ -14644,7 +14655,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -14693,7 +14704,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -14728,7 +14739,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -14743,7 +14754,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -14775,7 +14786,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -14790,7 +14801,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -14822,7 +14833,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -14837,7 +14848,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -14869,7 +14880,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -14884,7 +14895,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -14917,7 +14928,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -14932,7 +14943,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -14964,7 +14975,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -14979,7 +14990,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -15011,7 +15022,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -15026,7 +15037,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -15058,7 +15069,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -15073,7 +15084,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -15105,7 +15116,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -15120,7 +15131,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -15158,7 +15169,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15173,7 +15184,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -15205,7 +15216,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15220,7 +15231,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -15252,7 +15263,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -15263,7 +15274,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS, למעט סרגל הכלים של עמוד האוסף (assets/section-collection.css:170, 192, 201): שם לחצן "סינון" מוצג ראשון, המיון שני ומספר התוצאות שלישי, בעוד ב-DOM מספר התוצאות מופיע לפני המיון. מדובר בשלושה פקדים עצמאיים, ומספר התוצאות הוא אזור role="status" המוכרז בנפרד, ולכן להערכתנו אין פגיעה במשמעות - אך יש לאשר זאת בבדיקת קורא מסך.</t>
         </is>
@@ -15296,7 +15307,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15311,7 +15322,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -15344,7 +15355,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15359,7 +15370,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -15391,7 +15402,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -15406,7 +15417,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -15440,7 +15451,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15455,7 +15466,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -15487,7 +15498,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -15498,7 +15509,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -15530,7 +15541,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -15541,7 +15552,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -15576,7 +15587,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -15587,7 +15598,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -15619,7 +15630,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15634,7 +15645,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -15667,7 +15678,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -15682,7 +15693,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -15715,7 +15726,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15730,7 +15741,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -15762,7 +15773,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15777,7 +15788,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -15809,7 +15820,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15824,7 +15835,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -15856,7 +15867,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15871,7 +15882,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -15903,7 +15914,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -15914,7 +15925,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -15946,7 +15957,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -15961,7 +15972,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -15993,7 +16004,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16008,7 +16019,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -16040,7 +16051,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16055,7 +16066,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -16087,7 +16098,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16102,7 +16113,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -16134,7 +16145,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16149,7 +16160,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -16182,7 +16193,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16197,7 +16208,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -16229,7 +16240,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16244,7 +16255,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -16277,7 +16288,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16292,7 +16303,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -16325,7 +16336,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16340,7 +16351,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -16372,7 +16383,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16387,7 +16398,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -16419,7 +16430,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16434,7 +16445,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -16469,7 +16480,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16484,7 +16495,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -16516,7 +16527,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16531,7 +16542,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -16566,7 +16577,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -16581,7 +16592,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -16617,7 +16628,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -16628,7 +16639,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -16661,7 +16672,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16676,7 +16687,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -16827,7 +16838,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עמוד מוצר</t>
         </is>
@@ -16837,7 +16848,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/products/&lt;דוגמה&gt;</t>
         </is>
@@ -16852,7 +16863,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -16901,7 +16912,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -16936,7 +16947,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -16951,7 +16962,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -16983,7 +16994,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -16998,7 +17009,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -17030,7 +17041,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17045,7 +17056,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -17077,7 +17088,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17092,7 +17103,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -17125,7 +17136,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17140,7 +17151,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -17172,7 +17183,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17187,7 +17198,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -17219,7 +17230,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17234,7 +17245,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -17266,7 +17277,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17281,7 +17292,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -17313,7 +17324,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17328,7 +17339,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -17366,7 +17377,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17381,7 +17392,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -17413,7 +17424,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17428,7 +17439,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -17460,7 +17471,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -17471,7 +17482,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -17504,7 +17515,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17519,7 +17530,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -17552,7 +17563,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17567,7 +17578,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -17599,7 +17610,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17614,7 +17625,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -17648,7 +17659,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17663,7 +17674,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -17695,7 +17706,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -17706,7 +17717,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -17738,7 +17749,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -17749,7 +17760,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -17784,7 +17795,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -17795,7 +17806,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -17827,7 +17838,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17842,7 +17853,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -17875,7 +17886,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -17890,7 +17901,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -17923,7 +17934,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17938,7 +17949,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -17970,7 +17981,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -17985,7 +17996,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -18017,7 +18028,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18032,7 +18043,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -18064,7 +18075,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18079,7 +18090,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -18111,7 +18122,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -18122,7 +18133,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -18154,7 +18165,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18169,7 +18180,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -18201,7 +18212,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18216,7 +18227,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -18248,7 +18259,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18263,7 +18274,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -18295,7 +18306,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18310,7 +18321,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -18342,7 +18353,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18357,7 +18368,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -18390,7 +18401,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18405,7 +18416,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -18437,7 +18448,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18452,7 +18463,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -18485,7 +18496,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18500,7 +18511,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -18533,7 +18544,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18548,7 +18559,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -18580,7 +18591,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18595,7 +18606,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -18627,7 +18638,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18642,7 +18653,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -18677,7 +18688,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18692,7 +18703,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -18724,7 +18735,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18739,7 +18750,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -18774,7 +18785,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -18789,7 +18800,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -18825,7 +18836,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -18836,7 +18847,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -18869,7 +18880,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -18884,7 +18895,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -19035,7 +19046,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עגלת קניות</t>
         </is>
@@ -19045,7 +19056,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/cart</t>
         </is>
@@ -19060,7 +19071,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -19109,7 +19120,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -19144,7 +19155,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -19159,7 +19170,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>בעמוד זה אין תמונות תוכן; התמונה היחידה היא הלוגו שבכותרת, הנושא טקסט חלופי. שאר האמור בשורה זו נבדק ברמת התבנית כולה: נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -19191,7 +19202,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19206,7 +19217,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -19238,7 +19249,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19253,7 +19264,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -19285,7 +19296,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19300,7 +19311,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -19333,7 +19344,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19348,7 +19359,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -19380,7 +19391,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19395,7 +19406,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -19427,7 +19438,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19442,7 +19453,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -19474,7 +19485,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19489,7 +19500,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -19521,7 +19532,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19536,7 +19547,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -19574,7 +19585,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -19589,7 +19600,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -19621,7 +19632,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -19636,7 +19647,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -19668,7 +19679,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -19679,7 +19690,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -19712,7 +19723,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -19727,7 +19738,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -19760,7 +19771,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -19775,7 +19786,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -19807,7 +19818,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19822,7 +19833,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -19856,7 +19867,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -19871,7 +19882,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -19903,7 +19914,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -19914,7 +19925,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -19946,7 +19957,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="75" t="inlineStr">
+      <c r="F21" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -19961,7 +19972,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה תמונות מלבד הלוגו, הפטור מהקריטריון.</t>
         </is>
@@ -19996,7 +20007,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -20007,7 +20018,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -20039,7 +20050,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20054,7 +20065,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -20087,7 +20098,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -20102,7 +20113,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -20135,7 +20146,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20150,7 +20161,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -20182,7 +20193,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20197,7 +20208,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -20229,7 +20240,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20244,7 +20255,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -20276,7 +20287,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20291,7 +20302,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -20323,7 +20334,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -20334,7 +20345,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -20366,7 +20377,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20381,7 +20392,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -20413,7 +20424,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20428,7 +20439,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -20460,7 +20471,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20475,7 +20486,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -20507,7 +20518,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20522,7 +20533,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -20554,7 +20565,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20569,7 +20580,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -20602,7 +20613,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20617,7 +20628,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -20649,7 +20660,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20664,7 +20675,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -20697,7 +20708,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20712,7 +20723,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -20745,7 +20756,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20760,7 +20771,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -20792,7 +20803,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20807,7 +20818,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -20839,7 +20850,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20854,7 +20865,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -20889,7 +20900,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20904,7 +20915,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -20936,7 +20947,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -20951,7 +20962,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -20986,7 +20997,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="73" t="inlineStr">
+      <c r="F43" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -21001,7 +21012,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>הוספה לעגלה, שינוי כמות והסרה הפיכים במלואם בכל שלב, ותהליך התשלום של Shopify כולל שלב סקירה ואישור של ההזמנה לפני החיוב.</t>
         </is>
@@ -21037,7 +21048,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -21048,7 +21059,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -21081,7 +21092,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -21096,7 +21107,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -21247,7 +21258,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>תוצאות חיפוש</t>
         </is>
@@ -21257,7 +21268,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/search</t>
         </is>
@@ -21272,7 +21283,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -21321,7 +21332,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -21356,7 +21367,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -21371,7 +21382,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -21403,7 +21414,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21418,7 +21429,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -21450,7 +21461,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21465,7 +21476,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -21497,7 +21508,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21512,7 +21523,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -21545,7 +21556,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21560,7 +21571,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -21592,7 +21603,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21607,7 +21618,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -21639,7 +21650,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21654,7 +21665,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -21686,7 +21697,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21701,7 +21712,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -21733,7 +21744,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -21748,7 +21759,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -21786,7 +21797,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -21801,7 +21812,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -21833,7 +21844,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -21848,7 +21859,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -21880,7 +21891,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -21891,7 +21902,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -21924,7 +21935,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -21939,7 +21950,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -21972,7 +21983,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -21987,7 +21998,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -22019,7 +22030,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -22034,7 +22045,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -22068,7 +22079,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22083,7 +22094,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -22115,7 +22126,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -22126,7 +22137,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -22158,7 +22169,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -22169,7 +22180,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -22204,7 +22215,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -22215,7 +22226,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -22247,7 +22258,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22262,7 +22273,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -22295,7 +22306,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -22310,7 +22321,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -22343,7 +22354,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22358,7 +22369,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -22390,7 +22401,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22405,7 +22416,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -22437,7 +22448,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22452,7 +22463,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -22484,7 +22495,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22499,7 +22510,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -22531,7 +22542,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -22542,7 +22553,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -22574,7 +22585,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22589,7 +22600,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -22621,7 +22632,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22636,7 +22647,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -22668,7 +22679,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22683,7 +22694,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -22715,7 +22726,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22730,7 +22741,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -22762,7 +22773,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22777,7 +22788,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -22810,7 +22821,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22825,7 +22836,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -22857,7 +22868,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22872,7 +22883,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -22905,7 +22916,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22920,7 +22931,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -22953,7 +22964,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -22968,7 +22979,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -23000,7 +23011,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -23015,7 +23026,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -23047,7 +23058,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -23062,7 +23073,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -23097,7 +23108,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -23112,7 +23123,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -23144,7 +23155,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -23159,7 +23170,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -23194,7 +23205,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23209,7 +23220,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -23245,7 +23256,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -23256,7 +23267,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -23289,7 +23300,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -23304,7 +23315,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -23455,7 +23466,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עמוד תוכן (מי אנחנו, שאלות ותשובות)</t>
         </is>
@@ -23465,7 +23476,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/pages/&lt;דוגמה&gt;</t>
         </is>
@@ -23480,7 +23491,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -23529,7 +23540,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -23564,7 +23575,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -23579,7 +23590,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -23611,7 +23622,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23626,7 +23637,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. הערה נוספת: גוף עמוד זה נכתב בעורך התוכן של Shopify, שבו אפשר לשבץ נגן חיצוני; נכון למועד הבדיקה לא שובץ נגן כזה.</t>
         </is>
@@ -23658,7 +23669,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23673,7 +23684,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -23705,7 +23716,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23720,7 +23731,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -23753,7 +23764,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23768,7 +23779,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -23800,7 +23811,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23815,7 +23826,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -23847,7 +23858,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23862,7 +23873,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -23894,7 +23905,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23909,7 +23920,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -23941,7 +23952,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -23956,7 +23967,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -23994,7 +24005,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24009,7 +24020,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -24041,7 +24052,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24056,7 +24067,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -24088,7 +24099,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -24099,7 +24110,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -24132,7 +24143,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24147,7 +24158,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -24180,7 +24191,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24195,7 +24206,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -24227,7 +24238,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -24242,7 +24253,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -24276,7 +24287,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24291,7 +24302,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -24323,7 +24334,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -24334,7 +24345,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -24366,7 +24377,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="n"/>
+      <c r="F21" s="77" t="n"/>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -24377,7 +24388,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
         </is>
@@ -24412,7 +24423,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -24423,7 +24434,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -24455,7 +24466,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24470,7 +24481,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -24503,7 +24514,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -24518,7 +24529,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -24551,7 +24562,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24566,7 +24577,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -24598,7 +24609,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24613,7 +24624,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -24645,7 +24656,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24660,7 +24671,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -24692,7 +24703,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24707,7 +24718,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -24739,7 +24750,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -24750,7 +24761,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -24782,7 +24793,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24797,7 +24808,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -24829,7 +24840,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24844,7 +24855,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -24876,7 +24887,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24891,7 +24902,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -24923,7 +24934,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24938,7 +24949,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -24970,7 +24981,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -24985,7 +24996,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -25018,7 +25029,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25033,7 +25044,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -25065,7 +25076,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25080,7 +25091,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -25113,7 +25124,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25128,7 +25139,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -25161,7 +25172,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25176,7 +25187,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -25208,7 +25219,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25223,7 +25234,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -25255,7 +25266,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25270,7 +25281,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -25305,7 +25316,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25320,7 +25331,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -25352,7 +25363,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25367,7 +25378,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -25402,7 +25413,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -25417,7 +25428,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -25453,7 +25464,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -25464,7 +25475,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -25497,7 +25508,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25512,7 +25523,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>
@@ -25663,7 +25674,7 @@
           <t>שם העמוד / מסמך:</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="71" t="inlineStr">
         <is>
           <t>עמודי מדיניות, תקנון והצהרת נגישות</t>
         </is>
@@ -25673,7 +25684,7 @@
           <t>כתובת העמוד / מסמך (URL):</t>
         </is>
       </c>
-      <c r="D1" s="71" t="inlineStr">
+      <c r="D1" s="72" t="inlineStr">
         <is>
           <t>https://anshilo.com/policies/&lt;דוגמה&gt;</t>
         </is>
@@ -25688,7 +25699,7 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="I2" s="69" t="inlineStr">
+      <c r="I2" s="70" t="inlineStr">
         <is>
           <t>מקרא: תא ריק בעמודת "תוצאה" משמעו שהקריטריון טרם נבדק, והסיבה מופיעה בהערה. ראו גיליון "סיכום ומקרא".</t>
         </is>
@@ -25737,7 +25748,7 @@
           <t>הסבר על הקריטריון (באנגלית)</t>
         </is>
       </c>
-      <c r="I3" s="72" t="inlineStr">
+      <c r="I3" s="73" t="inlineStr">
         <is>
           <t>הערות הבדיקה, והראיה שעליה היא מבוססת</t>
         </is>
@@ -25772,7 +25783,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -25787,7 +25798,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I4" s="74" t="inlineStr">
+      <c r="I4" s="75" t="inlineStr">
         <is>
           <t>בעמוד זה אין תמונות תוכן; התמונה היחידה היא הלוגו שבכותרת, הנושא טקסט חלופי. שאר האמור בשורה זו נבדק ברמת התבנית כולה: נסרקו כל תבניות התבנית: 39 תגי img, לכולם מאפיין alt. בתמונות מוצר, אוסף וכתבה ה-alt נגזר מה-alt של המדיה, ובהיעדרו משם הפריט (snippets/product-card.liquid:100, snippets/product-media-gallery.liquid:134). 11 תמונות נושאות alt="" ביודעין: הן תמונות קישוט שלצדן מופיעה כבר כותרת טקסט גלויה, או שהן בתוך לחצן הנושא aria-label בעצמו (snippets/product-media-gallery.liquid:305), כך שקורא המסך אינו קורא אותן פעמיים. לתמונות המהוות קישור - הקישור עצמו נושא את שם הפריט. אין באתר תמונות מורכבות (תרשימים, גרפים) הדורשות תיאור ארוך. הערה: התאמת נוסח ה-alt לכל אחת מכ-1,900 תמונות המוצר היא שיקול תוכן ואינה ניתנת לאימות מתוך הקוד.</t>
         </is>
@@ -25819,7 +25830,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F5" s="75" t="inlineStr">
+      <c r="F5" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -25834,7 +25845,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I5" s="74" t="inlineStr">
+      <c r="I5" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. הערה נוספת: גוף עמוד זה נכתב בעורך התוכן של Shopify, שבו אפשר לשבץ נגן חיצוני; נכון למועד הבדיקה לא שובץ נגן כזה.</t>
         </is>
@@ -25866,7 +25877,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -25881,7 +25892,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I6" s="74" t="inlineStr">
+      <c r="I6" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש. אין באתר גם מבחן או תוכן המהווה חוויה חושית.</t>
         </is>
@@ -25913,7 +25924,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr">
+      <c r="F7" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -25928,7 +25939,7 @@
           <t>הסבר על קריטריון 1.1.1</t>
         </is>
       </c>
-      <c r="I7" s="74" t="inlineStr">
+      <c r="I7" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה מנגנון CAPTCHA.</t>
         </is>
@@ -25961,7 +25972,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -25976,7 +25987,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I8" s="74" t="inlineStr">
+      <c r="I8" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -26008,7 +26019,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -26023,7 +26034,7 @@
           <t>הסבר על קריטריון 1.2.1</t>
         </is>
       </c>
-      <c r="I9" s="74" t="inlineStr">
+      <c r="I9" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -26055,7 +26066,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -26070,7 +26081,7 @@
           <t>הסבר על קריטריון 1.2.2</t>
         </is>
       </c>
-      <c r="I10" s="74" t="inlineStr">
+      <c r="I10" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -26102,7 +26113,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -26117,7 +26128,7 @@
           <t>הסבר על קריטריון 1.2.3</t>
         </is>
       </c>
-      <c r="I11" s="74" t="inlineStr">
+      <c r="I11" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -26149,7 +26160,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -26164,7 +26175,7 @@
           <t>הסבר על קריטריון 1.2.5</t>
         </is>
       </c>
-      <c r="I12" s="74" t="inlineStr">
+      <c r="I12" s="75" t="inlineStr">
         <is>
           <t>לא נמצאה באתר מדיה מבוססת זמן. בתבנית אין נגן אודיו או וידאו, ובדגימה של 30 המוצרים שעודכנו לאחרונה כל פריטי המדיה הם מסוג IMAGE (נשלף מ-Shopify Admin API, שדה mediaContentType). אם יתווסף וידאו או אודיו לאתר - יש לבדוק שורה זו מחדש.</t>
         </is>
@@ -26202,7 +26213,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26217,7 +26228,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I13" s="74" t="inlineStr">
+      <c r="I13" s="75" t="inlineStr">
         <is>
           <t>קוד סמנטי מלא: main[role="main"] (layout/theme.liquid:291), header (sections/header.liquid:71), footer[role="contentinfo"] (sections/footer.liquid:51), nav עם aria-label לכל אזור ניווט, form[role="search"] לחיפוש. רשימות וקבוצות קישורים מסומנות ב-ul/ol. טבלאות: נסרקו כל הטבלאות בתבנית - לכולן תאי כותרת th עם scope. טפסים: נסרקו כל הפקדים - לא נמצא פקד ללא תווית (label, aria-label או aria-labelledby); בורר הווריאנטים מקובץ ב-fieldset עם legend (snippets/product-variant-picker.liquid:93). לא נמצא סימון תצוגתי במקום סמנטי (font, center, big, tt, bgcolor, align).</t>
         </is>
@@ -26249,7 +26260,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="73" t="inlineStr">
+      <c r="F14" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26264,7 +26275,7 @@
           <t>הסבר על קריטריון 1.3.1</t>
         </is>
       </c>
-      <c r="I14" s="74" t="inlineStr">
+      <c r="I14" s="75" t="inlineStr">
         <is>
           <t>הפרדה מלאה בין תוכן לתצוגה: כל העיצוב יושב בגיליונות סגנון חיצוניים. שימושי המאפיין style= שנותרו בתבנית מעבירים ערכי custom properties בלבד (למשל --nav-thumb-size), ואינם עיצוב בתוך התגית. לא נמצאו תגיות תצוגה (font, center, big, tt) ולא פריסה מבוססת טבלאות.</t>
         </is>
@@ -26296,7 +26307,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" s="76" t="n"/>
+      <c r="F15" s="77" t="n"/>
       <c r="G15" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.3.2</t>
@@ -26307,7 +26318,7 @@
           <t>הסבר על קריטריון 1.3.2</t>
         </is>
       </c>
-      <c r="I15" s="74" t="inlineStr">
+      <c r="I15" s="75" t="inlineStr">
         <is>
           <t>הטופס מחייב לבצע קריטריון זה בבדיקת קורא מסך, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: סדר ה-DOM תואם את סדר ההצגה, ולא נמצא שינוי סדר באמצעות CSS.</t>
         </is>
@@ -26340,7 +26351,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26355,7 +26366,7 @@
           <t>הסבר על קריטריון 1.3.3</t>
         </is>
       </c>
-      <c r="I16" s="74" t="inlineStr">
+      <c r="I16" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק בקובץ locales/he.default.json: אין באתר הוראה המסתמכת על צבע, על צורה, על מיקום על המסך או על צליל. אין הוראות מסוג "לחץ על הכפתור המרובע" או "קרא את הכתוב באדום".</t>
         </is>
@@ -26388,7 +26399,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26403,7 +26414,7 @@
           <t>הסבר על קריטריון 1.4.1</t>
         </is>
       </c>
-      <c r="I17" s="74" t="inlineStr">
+      <c r="I17" s="75" t="inlineStr">
         <is>
           <t>מידע אינו מועבר בצבע בלבד: תגי המצב נושאים טקסט ("מבצע", "אזל מהמלאי", "חדש"), וזמינות המוצר מנוסחת במילים ולא בנקודה צבעונית. קישורים: הפרש הניגודיות בין צבע הקישור (#D81E29) לטקסט הגוף (#16202F) נמדד 3.23:1 - מעל ה-3:1 שהקריטריון מתיר - ובנוסף הקישור נבדל במשקל גופן 600, מקבל קו תחתון בריחוף עכבר ומסגרת פוקוס בקבלת פוקוס (assets/base.css:91, 97, 105), כנדרש. קישורים בתוך גוף טקסט (.rte a) נושאים קו תחתון כברירת מחדל של הדפדפן. הערה לשיפור: קישור המונח בתוך פסקה בצבע המשני (#5B6779) נבדל ממנה ב-1.13:1 בלבד ומסתמך שם על משקל הגופן ועל ה-hover/focus בלבד; קו תחתון קבוע לכל הקישורים יסיר את התלות הזו.</t>
         </is>
@@ -26435,7 +26446,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -26450,7 +26461,7 @@
           <t>הסבר על קריטריון 1.4.2</t>
         </is>
       </c>
-      <c r="I18" s="74" t="inlineStr">
+      <c r="I18" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד אודיו המתנגן אוטומטית.</t>
         </is>
@@ -26484,7 +26495,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F19" s="73" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26499,7 +26510,7 @@
           <t>הסבר על קריטריון 1.4.3</t>
         </is>
       </c>
-      <c r="I19" s="74" t="inlineStr">
+      <c r="I19" s="75" t="inlineStr">
         <is>
           <t>נמדדו 36 שילובי הצבע שהתבנית מייצרת בפועל - לא רק ההגדרות הגולמיות, אלא גם הגוונים שהפריסה מחשבת במסננים color_mix ו-color_lighten. ארבעה שילובים נכשלו ותוקנו במסגרת בדיקה זו: צבע ההדגשה על גבי הרקע הוורוד הבהיר נמדד 4.47:1 ו-4.06:1, מתחת ל-4.5:1 הנדרש, והוחלף בגוון כהה יותר של אותו הגוון (6.07:1 ו-5.52:1) בקומפוננטות .btn--quiet, .badge--soft, .price__save, ווריאנט נבחר ותג "נבחרו" בסינון. כל שאר השילובים נמדדו 4.69:1 ומעלה, וטקסט הגוף 16.38:1. גבולות שאינם נושאי מידע ואייקונים נבדקו בנפרד מול דרישת ה-3:1 וחורגים ממנה לטובה.</t>
         </is>
@@ -26531,7 +26542,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F20" s="76" t="n"/>
+      <c r="F20" s="77" t="n"/>
       <c r="G20" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.4</t>
@@ -26542,7 +26553,7 @@
           <t>הסבר על קריטריון 1.4.4</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I20" s="75" t="inlineStr">
         <is>
           <t>דרושה בדיקה ידנית של הגדלה ל-200% בעמוד עצמו, וזו לא בוצעה - ולכן השורה נותרת ריקה. מה שכן נבדק: הטיפוגרפיה כולה מבוססת יחידות rem ולכן נגררת עם שינוי גודל הגופן, וכך גם עובדים צעדי הגדלת הטקסט שבתפריט הנגישות, המשנים את גודל הגופן של השורש (assets/accessibility.css:135); הערך היחיד בכל גיליונות הסגנון שהוגדר ב-px הוא תווית בתוך ציור SVG בעל viewBox, הנגררת עם הציור ואינה טקסט תוכן; ולא נמצא מכל טקסט בעל גובה קבוע שעלול לחתוך תוכן בהגדלה.</t>
         </is>
@@ -26574,7 +26585,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="75" t="inlineStr">
+      <c r="F21" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -26589,7 +26600,7 @@
           <t>הסבר על קריטריון 1.4.5</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה תמונות מלבד הלוגו, הפטור מהקריטריון.</t>
         </is>
@@ -26624,7 +26635,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F22" s="76" t="n"/>
+      <c r="F22" s="77" t="n"/>
       <c r="G22" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.1.1</t>
@@ -26635,7 +26646,7 @@
           <t>הסבר על קריטריון 2.1.1</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
+      <c r="I22" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני מלא על העמוד, והוא לא בוצע במלואו - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית; אין מטפל אירועים על אלמנט לא אינטראקטיבי (div/span עם onclick); כל הפקדים הם רכיבי HTML מקוריים - button, a, input, select, details/summary - ולא חיקויים; אין role="button" על אלמנט שאינו לחצן. נבדק בפועל בדפדפן: לוח החיפוש (פתיחה, הקלדה, בחירה, Escape, לחיצה בחוץ), רכיבי האקורדיון של תיאור המוצר ושאלות ומשלוחים, סרגל ההודעות וכפתור ההוספה לעגלה בכרטיס המוצר. טרם נבדקו ידנית: מגירת העגלה, מגירת הסינון, גלריית המוצר, ההזמנה המהירה וטפסי החשבון.</t>
         </is>
@@ -26667,7 +26678,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="F23" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26682,7 +26693,7 @@
           <t>הסבר על קריטריון 2.1.2</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
+      <c r="I23" s="75" t="inlineStr">
         <is>
           <t>המגירות (תפריט, עגלה, סינון) מלכידות פוקוס בכוונה, כמצופה מחלון מודאלי, אך המלכודת מסתובבת בין הרכיבים ואינה חוסמת יציאה: Escape סוגר את המגירה והפוקוס חוזר ללחצן שפתח אותה (assets/global.js:54-81, 126). נבדק בדפדפן עבור לוח החיפוש ורכיבי האקורדיון. לא נמצא בתבנית רכיב שניתן להיכנס אליו במקלדת ולא לצאת ממנו.</t>
         </is>
@@ -26715,7 +26726,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -26730,7 +26741,7 @@
           <t>הסבר על קריטריון 2.2.1</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
+      <c r="I24" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד הגבלת זמן לקריאה, לתגובה או להשלמת פעולה, ואין time out המוגדר בתבנית.</t>
         </is>
@@ -26763,7 +26774,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F25" s="73" t="inlineStr">
+      <c r="F25" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26778,7 +26789,7 @@
           <t>הסבר על קריטריון 2.2.2</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
+      <c r="I25" s="75" t="inlineStr">
         <is>
           <t>סרגל ההודעות שבראש כל עמוד מחליף את תוכנו על טיימר, ולכן הקריטריון רלוונטי בכל עמוד. עד לתיקון שבוצע בבדיקה זו לא היה ניתן לעצור אותו: גיליון סגנון אינו יכול לעצור setInterval, ולכן לחצן "עצירת אנימציות ותנועה באתר" שבתפריט הנגישות לא הגיע אליו כלל, וגם הגדרת מערכת ההפעלה נבדקה פעם אחת בלבד בעת טעינת העמוד. כיום הטיימר נגזר משלושה מקורות - בחירת המבקר בתפריט הנגישות, הגדרת הסוחר בתבנית והגדרת מערכת ההפעלה - ונבדק מחדש בכל הפעלה, ואירוע shilo:motion עוצר סבב שכבר בתנועה ברגע הלחיצה ומחזיר את הסרגל לשקופית הראשונה. נבדק ב-Chromium: 3 חילופי שקופית ב-1.1 שניות כשהתנועה מותרת, ו-0 חילופים לאחר הלחיצה, על פני יותר משלושה מרווחי טיימר. בנוסף הסרגל נעצר בריחוף עכבר ובקבלת פוקוס. אין בעמוד תוכן נגלל, מהבהב או מתעדכן אוטומטית אחר.</t>
         </is>
@@ -26810,7 +26821,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F26" s="73" t="inlineStr">
+      <c r="F26" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26825,7 +26836,7 @@
           <t>הסבר על קריטריון 2.3.1</t>
         </is>
       </c>
-      <c r="I26" s="74" t="inlineStr">
+      <c r="I26" s="75" t="inlineStr">
         <is>
           <t>אין באתר תוכן מהבהב או מרצד. אין אנימציה הפועלת בקצב העולה על שלוש פעמים בשנייה, ואין הבזקים בשטח או בעוצמה החורגים מ-general flash ו-red flash thresholds.</t>
         </is>
@@ -26857,7 +26868,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="73" t="inlineStr">
+      <c r="F27" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26872,7 +26883,7 @@
           <t>הסבר על קריטריון 2.4.1</t>
         </is>
       </c>
-      <c r="I27" s="74" t="inlineStr">
+      <c r="I27" s="75" t="inlineStr">
         <is>
           <t>קיים קישור "דילוג לתוכן", ראשון בסדר המקלדת, מוסתר עד לקבלת פוקוס ומוביל ישירות ל-#MainContent (layout/theme.liquid:278, 291). בנוסף אזורי הדף מסומנים ב-landmarks, המאפשרים לקורא מסך לדלג בין בלוקים ישירות.</t>
         </is>
@@ -26904,7 +26915,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="73" t="inlineStr">
+      <c r="F28" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -26919,7 +26930,7 @@
           <t>הסבר על קריטריון 2.4.2</t>
         </is>
       </c>
-      <c r="I28" s="74" t="inlineStr">
+      <c r="I28" s="75" t="inlineStr">
         <is>
           <t>תג &lt;title&gt; נבנה מ-page_title של Shopify, ייחודי לכל עמוד ומתאר את תוכנו; בעמודי רשימה נוספים אליו התג המסונן ומספר העמוד (layout/theme.liquid:20-23).</t>
         </is>
@@ -26951,7 +26962,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F29" s="76" t="n"/>
+      <c r="F29" s="77" t="n"/>
       <c r="G29" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 2.4.3</t>
@@ -26962,7 +26973,7 @@
           <t>הסבר על קריטריון 2.4.3</t>
         </is>
       </c>
-      <c r="I29" s="74" t="inlineStr">
+      <c r="I29" s="75" t="inlineStr">
         <is>
           <t>דרוש מעבר מקלדת ידני על העמוד, והוא לא בוצע - ולכן השורה נותרת ריקה. מה שכן נבדק: אין tabindex חיובי בשום מקום בתבנית, כך שסדר הפוקוס נגזר מסדר ה-DOM; שקופיות לא פעילות בסרגל ההודעות מקבלות tabindex="-1" כדי לא להשאיר קישורים מוסתרים בסדר המקלדת (assets/section-header.js); ובסינון מוצרים הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד עצמו אחריה, כך שהמשתמש אינו מושלך לראש העמוד (assets/facets.js:133-196).</t>
         </is>
@@ -26994,7 +27005,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F30" s="73" t="inlineStr">
+      <c r="F30" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27009,7 +27020,7 @@
           <t>הסבר על קריטריון 2.4.4</t>
         </is>
       </c>
-      <c r="I30" s="74" t="inlineStr">
+      <c r="I30" s="75" t="inlineStr">
         <is>
           <t>נסרקו כל מחרוזות הממשק: אין באתר קישור מסוג "לחץ כאן", "קרא עוד" או "כאן" ללא הקשר. קישורי מוצר, אוסף וכתבה נושאים את שם הפריט עצמו. הטקסט הכללי היחיד שנמצא הוא הלחצן "המשך" בעמוד ההתחברות, שמטרתו ברורה מהקשר העמוד שבו הוא יושב.</t>
         </is>
@@ -27041,7 +27052,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F31" s="73" t="inlineStr">
+      <c r="F31" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27056,7 +27067,7 @@
           <t>הסבר על קריטריון 2.4.5</t>
         </is>
       </c>
-      <c r="I31" s="74" t="inlineStr">
+      <c r="I31" s="75" t="inlineStr">
         <is>
           <t>קיימות יותר מדרך אחת להגיע לכל עמוד: מנוע חיפוש הזמין בכל עמוד ובאזור התמונה הראשי, המציג הצעות מוצרים תוך כדי ההקלדה; תפריט ראשי היררכי; תפריטי הכותרת התחתונה; ועמוד רשימת האוספים.</t>
         </is>
@@ -27088,7 +27099,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F32" s="73" t="inlineStr">
+      <c r="F32" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27103,7 +27114,7 @@
           <t>הסבר על קריטריון 2.4.6</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
+      <c r="I32" s="75" t="inlineStr">
         <is>
           <t>כל הכותרות והתוויות באתר מנוסחות בעברית ומבהירות את הנושא או המטרה. נבדק שכל שדה טופס משויך לתווית, וכל לחצן אייקון נושא שם נגיש.</t>
         </is>
@@ -27135,7 +27146,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F33" s="73" t="inlineStr">
+      <c r="F33" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27150,7 +27161,7 @@
           <t>הסבר על קריטריון 2.4.7</t>
         </is>
       </c>
-      <c r="I33" s="74" t="inlineStr">
+      <c r="I33" s="75" t="inlineStr">
         <is>
           <t>כלל :focus-visible גלובלי נותן לכל רכיב מסגרת 2px בצבע ההדגשה במרווח 2px (assets/base.css:105), בניגודיות 5.08:1 מול לבן - מעל דרישת ה-3:1 לסימון פוקוס. שדות קלט חסרי מסגרת עוטפים את עצמם בטבעת פוקוס ב-:focus-within. בבדיקה זו נמצא ותוקן חריג אחד: שדה הכמות ביטל את המסגרת ולא החזיר דבר במקומה, ולמעטפת שלו לא היה כלל :focus-within - כך שמעבר מקלדת אל שדה הכמות בעמוד המוצר, בעגלה, במגירת העגלה ובהזמנה המהירה לא הראה שום סימן פוקוס. נבדק ב-Chromium לאחר התיקון: מסגרת 2px בצבע ההדגשה, במרווח שלילי כדי שהמעטפת לא תחתוך אותה.</t>
         </is>
@@ -27182,7 +27193,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F34" s="73" t="inlineStr">
+      <c r="F34" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27197,7 +27208,7 @@
           <t>הסבר על קריטריון 2.4.10</t>
         </is>
       </c>
-      <c r="I34" s="74" t="inlineStr">
+      <c r="I34" s="75" t="inlineStr">
         <is>
           <t>כל מקטע (section) בעמוד נפתח בכותרת המזהה אותו, בהיררכיה יורדת מ-h1 של העמוד. כותרות המקטעים הן טקסט חי ולא תמונה.</t>
         </is>
@@ -27230,7 +27241,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27245,7 +27256,7 @@
           <t>הסבר על קריטריון 3.1.1</t>
         </is>
       </c>
-      <c r="I35" s="74" t="inlineStr">
+      <c r="I35" s="75" t="inlineStr">
         <is>
           <t>שפת העמוד מוגדרת בתג ה-HTML: &lt;html lang="he" dir="rtl"&gt;. השפה נגזרת מ-request.locale.iso_code והכיוון נקבע לפיה (layout/theme.liquid:9), כך שקורא מסך מבטא את הטקסט בעברית ובכיוון הנכון.</t>
         </is>
@@ -27277,7 +27288,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F36" s="73" t="inlineStr">
+      <c r="F36" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27292,7 +27303,7 @@
           <t>הסבר על קריטריון 3.1.2</t>
         </is>
       </c>
-      <c r="I36" s="74" t="inlineStr">
+      <c r="I36" s="75" t="inlineStr">
         <is>
           <t>טקסט הממשק כולו בעברית. שמות מותגים ומספרי דגם באותיות לטיניות (Makita, DHP453) הם שמות פרטיים ומונחים טכניים, הפטורים מהקריטריון. מספרי טלפון וכתובות דוא"ל עטופים ב-dir="ltr" עם בידוד דו-כיווני, כדי שייקראו בסדר שבו נכתבו. הערה: תיאורי מוצר המגיעים מיבואנים עלולים להכיל קטעים באנגלית; אם קיים קטע כזה, יש לסמנו ב-lang="en".</t>
         </is>
@@ -27325,7 +27336,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F37" s="73" t="inlineStr">
+      <c r="F37" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27340,7 +27351,7 @@
           <t>הסבר על קריטריון 3.2.1</t>
         </is>
       </c>
-      <c r="I37" s="74" t="inlineStr">
+      <c r="I37" s="75" t="inlineStr">
         <is>
           <t>קבלת פוקוס אינה גורמת לשינוי הקשר: לא נפתח חלון, לא מועבר מוקד ולא מתבצע מעבר עמוד. לוח הצעות החיפוש נפתח בקבלת פוקוס בשדה, וזו התנהגות ה-combobox המוגדרת ב-ARIA - הפוקוס נשאר בשדה והמשתמש יכול להתעלם מהלוח או לסגור אותו ב-Escape.</t>
         </is>
@@ -27373,7 +27384,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F38" s="73" t="inlineStr">
+      <c r="F38" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27388,7 +27399,7 @@
           <t>הסבר על קריטריון 3.2.2</t>
         </is>
       </c>
-      <c r="I38" s="74" t="inlineStr">
+      <c r="I38" s="75" t="inlineStr">
         <is>
           <t>שינוי ערך בסינון, במיון, בבורר הווריאנטים או בשדה הכמות מעדכן את התוצאות או את המחיר - זו ההתנהגות המצופה של הפקדים הללו ואינה שינוי הקשר: הפוקוס נשמר לפני החלפת ה-DOM ומוחזר לאותו פקד אחריה, ומספר התוצאות מוכרז לקורא מסך דרך אזור role="status" (assets/facets.js:133-196, 203). לא נפתח חלון ולא מתבצע מעבר עמוד אוטומטי.</t>
         </is>
@@ -27420,7 +27431,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F39" s="73" t="inlineStr">
+      <c r="F39" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27435,7 +27446,7 @@
           <t>הסבר על קריטריון 3.2.3</t>
         </is>
       </c>
-      <c r="I39" s="74" t="inlineStr">
+      <c r="I39" s="75" t="inlineStr">
         <is>
           <t>מנגנוני הניווט - כותרת עליונה, תפריט ראשי, חיפוש, עגלה וכותרת תחתונה - מופיעים באותו סדר ובאותו מקום בכל עמוד באתר, ונטענים מאותם מקטעים משותפים.</t>
         </is>
@@ -27467,7 +27478,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F40" s="73" t="inlineStr">
+      <c r="F40" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27482,7 +27493,7 @@
           <t>הסבר על קריטריון 3.2.4</t>
         </is>
       </c>
-      <c r="I40" s="74" t="inlineStr">
+      <c r="I40" s="75" t="inlineStr">
         <is>
           <t>רכיבים החוזרים בעמודים שונים מזוהים באופן זהה: אותו אייקון, אותו טקסט נגיש ואותה התנהגות ללחצן העגלה, לחיפוש, לתפריט הנגישות ולכפתור ההוספה לעגלה בכל מקום שבו הם מופיעים.</t>
         </is>
@@ -27517,7 +27528,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F41" s="73" t="inlineStr">
+      <c r="F41" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27532,7 +27543,7 @@
           <t>הסבר על קריטריון 3.3.1</t>
         </is>
       </c>
-      <c r="I41" s="74" t="inlineStr">
+      <c r="I41" s="75" t="inlineStr">
         <is>
           <t>הודעות שגיאה מוצגות כטקסט, יושבות בתוך אזור role="alert" ומקבלות פוקוס (tabindex="-1"), כך שקורא מסך מכריז עליהן מיד עם הופעתן. נוסח השגיאה וההצעה לתיקון לשדות המובנים מגיעים מ-Shopify. הודעות הצלחה יושבות ב-role="status".</t>
         </is>
@@ -27564,7 +27575,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F42" s="73" t="inlineStr">
+      <c r="F42" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27579,7 +27590,7 @@
           <t>הסבר על קריטריון 3.3.2</t>
         </is>
       </c>
-      <c r="I42" s="74" t="inlineStr">
+      <c r="I42" s="75" t="inlineStr">
         <is>
           <t>כל שדה שהמשתמש נדרש למלא נושא תווית גלויה המשויכת אליו, ושדות חובה מסומנים. נסרקו כל הפקדים בתבנית ולא נמצא שדה המסתמך על placeholder בלבד כתווית.</t>
         </is>
@@ -27614,7 +27625,7 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="76" t="inlineStr">
         <is>
           <t>לא רלוונטי</t>
         </is>
@@ -27629,7 +27640,7 @@
           <t>הסבר על קריטריון 3.3.4</t>
         </is>
       </c>
-      <c r="I43" s="74" t="inlineStr">
+      <c r="I43" s="75" t="inlineStr">
         <is>
           <t>אין בעמוד זה טופס הגורר התחייבות משפטית, פעולה פיננסית או שינוי ומחיקה של נתוני משתמש.</t>
         </is>
@@ -27665,7 +27676,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
+      <c r="F44" s="77" t="n"/>
       <c r="G44" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 4.1.1</t>
@@ -27676,7 +27687,7 @@
           <t>הסבר על קריטריון 4.1.1</t>
         </is>
       </c>
-      <c r="I44" s="74" t="inlineStr">
+      <c r="I44" s="75" t="inlineStr">
         <is>
           <t>דרושה הרצת מאמת HTML (W3C Validator) על העמוד כפי שהוא מורכב בפועל, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לאתר החי, ולכן לא ניתן לאמת תגי פתיחה וסגירה, מאפיינים כפולים וקינון נכון בפלט המלא. מה שכן נבדק, על כל התבניות: אין מזהה id החוזר פעמיים באותו עמוד - שני מזהים חוזרים אותרו ואומתו כמופיעים בענפי if בלעדיים או בשתי פריסות שונות, ולא יחד; ואין id קבוע בתוך לולאה, שהיה מייצר כפילות בכל חזרה.</t>
         </is>
@@ -27709,7 +27720,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F45" s="73" t="inlineStr">
+      <c r="F45" s="74" t="inlineStr">
         <is>
           <t>תקין</t>
         </is>
@@ -27724,7 +27735,7 @@
           <t>הסבר על קריטריון 4.2.1</t>
         </is>
       </c>
-      <c r="I45" s="74" t="inlineStr">
+      <c r="I45" s="75" t="inlineStr">
         <is>
           <t>לכל לחצן אייקון יש aria-label; רכיבים נפתחים נושאים aria-expanded ו-aria-controls ומעדכנים אותם בזמן אמת; שדה החיפוש בנוי כתבנית combobox עם aria-expanded, aria-controls ואזור role="status" להכרזת מספר התוצאות; אריחי גלריית המוצר הם button עם aria-label ו-aria-current. אין בתבנית עצמה תג iframe או frame. הערה: אפליקציות צד שלישי המותקנות בחנות עלולות להזריק iframe משלהן - אם קיים כזה, יש לוודא שהוא נושא מאפיין title.</t>
         </is>

--- a/theme/accessibility/anshilo-accessibility-form.xlsx
+++ b/theme/accessibility/anshilo-accessibility-form.xlsx
@@ -314,7 +314,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
@@ -529,6 +529,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2014,7 +2017,7 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>דרושה בדיקה חזותית של התמונות בעמוד זה, וזו לא בוצעה - ולכן השורה נותרת ריקה. הערה: בתמונות מוצר באתר נמצא טקסט צרוב, ראו את שורה זו בגיליונות עמוד הבית, הקטגוריה, המוצר, החיפוש והעגלה.</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6429,7 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>דרושה בדיקה חזותית של התמונות בעמוד זה, וזו לא בוצעה - ולכן השורה נותרת ריקה. הערה: בתמונות מוצר באתר נמצא טקסט צרוב, ראו את שורה זו בגיליונות עמוד הבית, הקטגוריה, המוצר, החיפוש והעגלה.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8637,7 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>דרושה בדיקה חזותית של התמונות בעמוד זה, וזו לא בוצעה - ולכן השורה נותרת ריקה. הערה: בתמונות מוצר באתר נמצא טקסט צרוב, ראו את שורה זו בגיליונות עמוד הבית, הקטגוריה, המוצר, החיפוש והעגלה.</t>
         </is>
       </c>
     </row>
@@ -11814,7 +11817,7 @@
       </c>
       <c r="B10" s="60" t="inlineStr">
         <is>
-          <t>נבדק, ונמצא שאינו עומד בקריטריון. לא נותרו כאלה: ארבעה כשלי ניגודיות, כשל בסימון הפוקוס בשדה הכמות וכשל בעצירת התנועה בסרגל ההודעות נמצאו במהלך הבדיקה ותוקנו.</t>
+          <t>נבדק, ונמצא שאינו עומד בקריטריון, וטרם תוקן. כרגע אחד: קריטריון 1.4.5 - טקסט צרוב בתמונות מוצר, ובכללו מחיר ותנאי מבצע הקיימים כפיקסלים בלבד. ההערה מפרטת את הקבצים ואת הטקסט המדויק. כשלים נוספים שנמצאו במהלך הבדיקה כבר תוקנו ולכן אינם מופיעים כאן - ראו "מה תוקן במהלך הבדיקה".</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11901,7 @@
       </c>
       <c r="C16" s="66">
         <f>COUNTIF('עמוד הבית'!$F$4:$F$45,"לא תקין")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="66">
         <f>COUNTIF('עמוד הבית'!$F$4:$F$45,"לא רלוונטי")</f>
@@ -11906,7 +11909,7 @@
       </c>
       <c r="E16" s="66">
         <f>COUNTBLANK('עמוד הבית'!$F$4:$F$45)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" s="66">
         <f>SUM(B16:E16)</f>
@@ -11914,7 +11917,7 @@
       </c>
       <c r="G16" s="60" t="inlineStr">
         <is>
-          <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
+          <t>1.3.2, 1.4.4, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11933,7 @@
       </c>
       <c r="C17" s="66">
         <f>COUNTIF('עמוד קטגוריה'!$F$4:$F$45,"לא תקין")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="66">
         <f>COUNTIF('עמוד קטגוריה'!$F$4:$F$45,"לא רלוונטי")</f>
@@ -11938,7 +11941,7 @@
       </c>
       <c r="E17" s="66">
         <f>COUNTBLANK('עמוד קטגוריה'!$F$4:$F$45)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="66">
         <f>SUM(B17:E17)</f>
@@ -11946,7 +11949,7 @@
       </c>
       <c r="G17" s="60" t="inlineStr">
         <is>
-          <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
+          <t>1.3.2, 1.4.4, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11965,7 @@
       </c>
       <c r="C18" s="66">
         <f>COUNTIF('עמוד מוצר'!$F$4:$F$45,"לא תקין")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="66">
         <f>COUNTIF('עמוד מוצר'!$F$4:$F$45,"לא רלוונטי")</f>
@@ -11970,7 +11973,7 @@
       </c>
       <c r="E18" s="66">
         <f>COUNTBLANK('עמוד מוצר'!$F$4:$F$45)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="66">
         <f>SUM(B18:E18)</f>
@@ -11978,7 +11981,7 @@
       </c>
       <c r="G18" s="60" t="inlineStr">
         <is>
-          <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
+          <t>1.3.2, 1.4.4, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
@@ -11994,11 +11997,11 @@
       </c>
       <c r="C19" s="66">
         <f>COUNTIF('עגלת קניות'!$F$4:$F$45,"לא תקין")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="66">
         <f>COUNTIF('עגלת קניות'!$F$4:$F$45,"לא רלוונטי")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="66">
         <f>COUNTBLANK('עגלת קניות'!$F$4:$F$45)</f>
@@ -12026,7 +12029,7 @@
       </c>
       <c r="C20" s="66">
         <f>COUNTIF('תוצאות חיפוש'!$F$4:$F$45,"לא תקין")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="66">
         <f>COUNTIF('תוצאות חיפוש'!$F$4:$F$45,"לא רלוונטי")</f>
@@ -12034,7 +12037,7 @@
       </c>
       <c r="E20" s="66">
         <f>COUNTBLANK('תוצאות חיפוש'!$F$4:$F$45)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" s="66">
         <f>SUM(B20:E20)</f>
@@ -12042,7 +12045,7 @@
       </c>
       <c r="G20" s="60" t="inlineStr">
         <is>
-          <t>1.3.2, 1.4.4, 1.4.5, 2.1.1, 2.4.3, 4.1.1</t>
+          <t>1.3.2, 1.4.4, 2.1.1, 2.4.3, 4.1.1</t>
         </is>
       </c>
     </row>
@@ -12250,15 +12253,15 @@
       </c>
       <c r="C27" s="68">
         <f>SUM(C16:C26)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D27" s="68">
         <f>SUM(D16:D26)</f>
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E27" s="68">
         <f>SUM(E16:E26)</f>
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F27" s="68">
         <f>SUM(F16:F26)</f>
@@ -13333,7 +13336,11 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="77" t="n"/>
+      <c r="F21" s="78" t="inlineStr">
+        <is>
+          <t>לא תקין</t>
+        </is>
+      </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -13346,7 +13353,12 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>לא תקין. נבדק חזותית באתר החי, ונמצא טקסט "צרוב" בתמונות מוצר - כלומר טקסט שקיים כפיקסלים בלבד ואינו קיים בשום צורת טקסט. שלוש דוגמאות מאומתות:
+(1) "סט אימפקט + פטישון 2 מקיטה", הקובץ WhatsAppImage2025-11-23at20.17.20.jpg בגודל 1200x1200: "יבואן רשמי ארגנטולס", "MAKITA", "סט כלים אימפקט + פטישון", "1699 ש''ח", "משלוח חינם", "כולל מע''מ", "עד גמר המלאי", "DHR202", "DTD152", "2 סוללות 5AH", "מטען מהיר", "ט.ל.ח", "החברה רשאית להפסיק את המבצע בכל רגע". ה-alt בעמוד הבית ריק, ובעמוד המוצר הוא שם המוצר בלבד - כך שהמחיר, תנאי המבצע והסייג המשפטי אינם נגישים כלל.
+(2) "עגלת משא 2 מצבים סטנלי", הקובץ 25.png בגודל 1080x1080, alt="": "מבצע!", "מצב שכיבה 150 ק''ג", "מצב עמידה 70 ק''ג", "שנתיים אחריות", "רק ב-359 ש''ח כולל מע''מ", "עד גמר המלאי", "STANLEY".
+(3) תג "יבואן רשמי דלקו", הקובץ 1708642472037-673720443-12334567891011121314.png בגודל 320x320, alt="דלקו מילווקי": "יבואן רשמי", "DELCO", "דלקו יבואנים בע''מ", "Milwaukee", "Nothing but HEAVY DUTY". הלוגואים פטורים מהקריטריון, אך "יבואן רשמי" ו"דלקו יבואנים בע''מ" הם מידע שאינו מופיע ב-alt.
+חמור מעצם ההפרה: מחיר ותנאי מבצע הקיימים כפיקסלים בלבד אינם זמינים לקורא מסך, וזו גם חשיפה צרכנית ולא רק נגישותית. התיקון הנכון אינו הוספת המחיר ל-alt - מחיר שיוקלד ל-alt יתיישן ויטעה - אלא הפקת התמונות בלי הטקסט המסחרי, והצגת המחיר, תג המבצע ותנאי המשלוח כטקסט חי, כפי שהתבנית עושה ממילא.
+תמונות אלה הן נתוני קטלוג ולכן הממצא תקף בכל ערכת עיצוב. תמונת הבאנר בעמוד הבית נבדקה בנפרד ונמצאה תקינה: הטקסט היחיד בה הוא שילוט פיזי בתוך צילום של המחסן, שנופל תחת חריג טקסט אגבי וחריג לוגו, והכותרת והכפתורים שמעליה הם טקסט חי.</t>
         </is>
       </c>
     </row>
@@ -15541,7 +15553,11 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="77" t="n"/>
+      <c r="F21" s="78" t="inlineStr">
+        <is>
+          <t>לא תקין</t>
+        </is>
+      </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -15554,7 +15570,12 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>לא תקין. נבדק חזותית באתר החי, ונמצא טקסט "צרוב" בתמונות מוצר - כלומר טקסט שקיים כפיקסלים בלבד ואינו קיים בשום צורת טקסט. שלוש דוגמאות מאומתות:
+(1) "סט אימפקט + פטישון 2 מקיטה", הקובץ WhatsAppImage2025-11-23at20.17.20.jpg בגודל 1200x1200: "יבואן רשמי ארגנטולס", "MAKITA", "סט כלים אימפקט + פטישון", "1699 ש''ח", "משלוח חינם", "כולל מע''מ", "עד גמר המלאי", "DHR202", "DTD152", "2 סוללות 5AH", "מטען מהיר", "ט.ל.ח", "החברה רשאית להפסיק את המבצע בכל רגע". ה-alt בעמוד הבית ריק, ובעמוד המוצר הוא שם המוצר בלבד - כך שהמחיר, תנאי המבצע והסייג המשפטי אינם נגישים כלל.
+(2) "עגלת משא 2 מצבים סטנלי", הקובץ 25.png בגודל 1080x1080, alt="": "מבצע!", "מצב שכיבה 150 ק''ג", "מצב עמידה 70 ק''ג", "שנתיים אחריות", "רק ב-359 ש''ח כולל מע''מ", "עד גמר המלאי", "STANLEY".
+(3) תג "יבואן רשמי דלקו", הקובץ 1708642472037-673720443-12334567891011121314.png בגודל 320x320, alt="דלקו מילווקי": "יבואן רשמי", "DELCO", "דלקו יבואנים בע''מ", "Milwaukee", "Nothing but HEAVY DUTY". הלוגואים פטורים מהקריטריון, אך "יבואן רשמי" ו"דלקו יבואנים בע''מ" הם מידע שאינו מופיע ב-alt.
+חמור מעצם ההפרה: מחיר ותנאי מבצע הקיימים כפיקסלים בלבד אינם זמינים לקורא מסך, וזו גם חשיפה צרכנית ולא רק נגישותית. התיקון הנכון אינו הוספת המחיר ל-alt - מחיר שיוקלד ל-alt יתיישן ויטעה - אלא הפקת התמונות בלי הטקסט המסחרי, והצגת המחיר, תג המבצע ותנאי המשלוח כטקסט חי, כפי שהתבנית עושה ממילא.
+תמונות אלה הן נתוני קטלוג ולכן הממצא תקף בכל ערכת עיצוב. תמונת הבאנר בעמוד הבית נבדקה בנפרד ונמצאה תקינה: הטקסט היחיד בה הוא שילוט פיזי בתוך צילום של המחסן, שנופל תחת חריג טקסט אגבי וחריג לוגו, והכותרת והכפתורים שמעליה הם טקסט חי.</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17770,11 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="77" t="n"/>
+      <c r="F21" s="78" t="inlineStr">
+        <is>
+          <t>לא תקין</t>
+        </is>
+      </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -17762,7 +17787,12 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>לא תקין. נבדק חזותית באתר החי, ונמצא טקסט "צרוב" בתמונות מוצר - כלומר טקסט שקיים כפיקסלים בלבד ואינו קיים בשום צורת טקסט. שלוש דוגמאות מאומתות:
+(1) "סט אימפקט + פטישון 2 מקיטה", הקובץ WhatsAppImage2025-11-23at20.17.20.jpg בגודל 1200x1200: "יבואן רשמי ארגנטולס", "MAKITA", "סט כלים אימפקט + פטישון", "1699 ש''ח", "משלוח חינם", "כולל מע''מ", "עד גמר המלאי", "DHR202", "DTD152", "2 סוללות 5AH", "מטען מהיר", "ט.ל.ח", "החברה רשאית להפסיק את המבצע בכל רגע". ה-alt בעמוד הבית ריק, ובעמוד המוצר הוא שם המוצר בלבד - כך שהמחיר, תנאי המבצע והסייג המשפטי אינם נגישים כלל.
+(2) "עגלת משא 2 מצבים סטנלי", הקובץ 25.png בגודל 1080x1080, alt="": "מבצע!", "מצב שכיבה 150 ק''ג", "מצב עמידה 70 ק''ג", "שנתיים אחריות", "רק ב-359 ש''ח כולל מע''מ", "עד גמר המלאי", "STANLEY".
+(3) תג "יבואן רשמי דלקו", הקובץ 1708642472037-673720443-12334567891011121314.png בגודל 320x320, alt="דלקו מילווקי": "יבואן רשמי", "DELCO", "דלקו יבואנים בע''מ", "Milwaukee", "Nothing but HEAVY DUTY". הלוגואים פטורים מהקריטריון, אך "יבואן רשמי" ו"דלקו יבואנים בע''מ" הם מידע שאינו מופיע ב-alt.
+חמור מעצם ההפרה: מחיר ותנאי מבצע הקיימים כפיקסלים בלבד אינם זמינים לקורא מסך, וזו גם חשיפה צרכנית ולא רק נגישותית. התיקון הנכון אינו הוספת המחיר ל-alt - מחיר שיוקלד ל-alt יתיישן ויטעה - אלא הפקת התמונות בלי הטקסט המסחרי, והצגת המחיר, תג המבצע ותנאי המשלוח כטקסט חי, כפי שהתבנית עושה ממילא.
+תמונות אלה הן נתוני קטלוג ולכן הממצא תקף בכל ערכת עיצוב. תמונת הבאנר בעמוד הבית נבדקה בנפרד ונמצאה תקינה: הטקסט היחיד בה הוא שילוט פיזי בתוך צילום של המחסן, שנופל תחת חריג טקסט אגבי וחריג לוגו, והכותרת והכפתורים שמעליה הם טקסט חי.</t>
         </is>
       </c>
     </row>
@@ -19957,9 +19987,9 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="76" t="inlineStr">
-        <is>
-          <t>לא רלוונטי</t>
+      <c r="F21" s="78" t="inlineStr">
+        <is>
+          <t>לא תקין</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
@@ -19974,7 +20004,12 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>אין בעמוד זה תמונות מלבד הלוגו, הפטור מהקריטריון.</t>
+          <t>לא תקין. נבדק חזותית באתר החי, ונמצא טקסט "צרוב" בתמונות מוצר - כלומר טקסט שקיים כפיקסלים בלבד ואינו קיים בשום צורת טקסט. שלוש דוגמאות מאומתות:
+(1) "סט אימפקט + פטישון 2 מקיטה", הקובץ WhatsAppImage2025-11-23at20.17.20.jpg בגודל 1200x1200: "יבואן רשמי ארגנטולס", "MAKITA", "סט כלים אימפקט + פטישון", "1699 ש''ח", "משלוח חינם", "כולל מע''מ", "עד גמר המלאי", "DHR202", "DTD152", "2 סוללות 5AH", "מטען מהיר", "ט.ל.ח", "החברה רשאית להפסיק את המבצע בכל רגע". ה-alt בעמוד הבית ריק, ובעמוד המוצר הוא שם המוצר בלבד - כך שהמחיר, תנאי המבצע והסייג המשפטי אינם נגישים כלל.
+(2) "עגלת משא 2 מצבים סטנלי", הקובץ 25.png בגודל 1080x1080, alt="": "מבצע!", "מצב שכיבה 150 ק''ג", "מצב עמידה 70 ק''ג", "שנתיים אחריות", "רק ב-359 ש''ח כולל מע''מ", "עד גמר המלאי", "STANLEY".
+(3) תג "יבואן רשמי דלקו", הקובץ 1708642472037-673720443-12334567891011121314.png בגודל 320x320, alt="דלקו מילווקי": "יבואן רשמי", "DELCO", "דלקו יבואנים בע''מ", "Milwaukee", "Nothing but HEAVY DUTY". הלוגואים פטורים מהקריטריון, אך "יבואן רשמי" ו"דלקו יבואנים בע''מ" הם מידע שאינו מופיע ב-alt.
+חמור מעצם ההפרה: מחיר ותנאי מבצע הקיימים כפיקסלים בלבד אינם זמינים לקורא מסך, וזו גם חשיפה צרכנית ולא רק נגישותית. התיקון הנכון אינו הוספת המחיר ל-alt - מחיר שיוקלד ל-alt יתיישן ויטעה - אלא הפקת התמונות בלי הטקסט המסחרי, והצגת המחיר, תג המבצע ותנאי המשלוח כטקסט חי, כפי שהתבנית עושה ממילא.
+תמונות אלה הן נתוני קטלוג ולכן הממצא תקף בכל ערכת עיצוב. תמונת הבאנר בעמוד הבית נבדקה בנפרד ונמצאה תקינה: הטקסט היחיד בה הוא שילוט פיזי בתוך צילום של המחסן, שנופל תחת חריג טקסט אגבי וחריג לוגו, והכותרת והכפתורים שמעליה הם טקסט חי.</t>
         </is>
       </c>
     </row>
@@ -22169,7 +22204,11 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="F21" s="77" t="n"/>
+      <c r="F21" s="78" t="inlineStr">
+        <is>
+          <t>לא תקין</t>
+        </is>
+      </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
           <t>טכניקות לביצוע קריטריון 1.4.5</t>
@@ -22182,7 +22221,12 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>לא תקין. נבדק חזותית באתר החי, ונמצא טקסט "צרוב" בתמונות מוצר - כלומר טקסט שקיים כפיקסלים בלבד ואינו קיים בשום צורת טקסט. שלוש דוגמאות מאומתות:
+(1) "סט אימפקט + פטישון 2 מקיטה", הקובץ WhatsAppImage2025-11-23at20.17.20.jpg בגודל 1200x1200: "יבואן רשמי ארגנטולס", "MAKITA", "סט כלים אימפקט + פטישון", "1699 ש''ח", "משלוח חינם", "כולל מע''מ", "עד גמר המלאי", "DHR202", "DTD152", "2 סוללות 5AH", "מטען מהיר", "ט.ל.ח", "החברה רשאית להפסיק את המבצע בכל רגע". ה-alt בעמוד הבית ריק, ובעמוד המוצר הוא שם המוצר בלבד - כך שהמחיר, תנאי המבצע והסייג המשפטי אינם נגישים כלל.
+(2) "עגלת משא 2 מצבים סטנלי", הקובץ 25.png בגודל 1080x1080, alt="": "מבצע!", "מצב שכיבה 150 ק''ג", "מצב עמידה 70 ק''ג", "שנתיים אחריות", "רק ב-359 ש''ח כולל מע''מ", "עד גמר המלאי", "STANLEY".
+(3) תג "יבואן רשמי דלקו", הקובץ 1708642472037-673720443-12334567891011121314.png בגודל 320x320, alt="דלקו מילווקי": "יבואן רשמי", "DELCO", "דלקו יבואנים בע''מ", "Milwaukee", "Nothing but HEAVY DUTY". הלוגואים פטורים מהקריטריון, אך "יבואן רשמי" ו"דלקו יבואנים בע''מ" הם מידע שאינו מופיע ב-alt.
+חמור מעצם ההפרה: מחיר ותנאי מבצע הקיימים כפיקסלים בלבד אינם זמינים לקורא מסך, וזו גם חשיפה צרכנית ולא רק נגישותית. התיקון הנכון אינו הוספת המחיר ל-alt - מחיר שיוקלד ל-alt יתיישן ויטעה - אלא הפקת התמונות בלי הטקסט המסחרי, והצגת המחיר, תג המבצע ותנאי המשלוח כטקסט חי, כפי שהתבנית עושה ממילא.
+תמונות אלה הן נתוני קטלוג ולכן הממצא תקף בכל ערכת עיצוב. תמונת הבאנר בעמוד הבית נבדקה בנפרד ונמצאה תקינה: הטקסט היחיד בה הוא שילוט פיזי בתוך צילום של המחסן, שנופל תחת חריג טקסט אגבי וחריג לוגו, והכותרת והכפתורים שמעליה הם טקסט חי.</t>
         </is>
       </c>
     </row>
@@ -24390,7 +24434,7 @@
       </c>
       <c r="I21" s="75" t="inlineStr">
         <is>
-          <t>דרושה בדיקה חזותית של התמונות שהועלו לחנות, וזו לא בוצעה: סביבת הבדיקה חסומה מהגעה לתמונות עצמן - ולכן השורה נותרת ריקה. מה שכן ידוע: התבנית מציגה כותרות, כפתורים ומחירים כטקסט חי ולא כתמונה. יש לוודא שבתמונות הבאנר והאריחים אין טקסט "צרוב" שאפשר היה להציג כטקסט חי. הלוגו פטור על פי הקריטריון.</t>
+          <t>דרושה בדיקה חזותית של התמונות בעמוד זה, וזו לא בוצעה - ולכן השורה נותרת ריקה. הערה: בתמונות מוצר באתר נמצא טקסט צרוב, ראו את שורה זו בגיליונות עמוד הבית, הקטגוריה, המוצר, החיפוש והעגלה.</t>
         </is>
       </c>
     </row>
